--- a/PS_new_options.xlsx
+++ b/PS_new_options.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liming/Desktop/LLM&amp;SJT/teacher/final_submittion/数据包/content_validity/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liming/Desktop/LLM&amp;SJT/teacher/final_submittion/content_validity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD9C491-0B2A-334C-9E71-3DFBA05A02F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3ADB92-76EE-4A4E-8045-F1424414AF3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="500" windowWidth="27720" windowHeight="16900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="632">
   <si>
     <t>scenario</t>
   </si>
@@ -1325,10 +1325,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>As the head teacher, you receive notice from the school that an emergency fire drill will be held this Friday. You need to ensure that all students can evacuate the classroom in an orderly and safe manner and reach the designated assembly place in a short time . What would you do in this situation?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>Immediately inform students of the drill arrangements and emphasize the importance and steps of the drill.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -1338,6 +1334,898 @@
   </si>
   <si>
     <t>Check the classroom's emergency exits to ensure they are clear and unobstructed.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>你作为班主任，接到学校通知，本周五要举行一次突发性的防火演习。你需要在短时间内确保所有学生都能有序、安全地撤离教室，并到达指定的集合地点。在这种情况下，你会怎么做？</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>You receive notice from the school that an emergency fire drill will be held this Friday. You need to ensure that all students can evacuate the classroom in an orderly and safe manner and reach the designated assembly place in a short time . What would you do in this situation?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Provide a brief fire safety education session before the drill to raise students' safety awareness.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Once at the assembly point, promptly conduct a headcount to ensure no one is missing.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Notify students that a fire drill will take place and ask them to be prepared.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Follow the school's unified arrangements and organize an orderly evacuation of students.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>During the evacuation, remind students to stay calm and avoid panicking.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Designate several students as assistants to help manage the evacuation order.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>After the evacuation, discuss with students about issues that arose during the drill and how to improve.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wait until just before the drill starts to inform students, to prevent them from becoming anxious in advance.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Let students decide their own evacuation routes and methods to develop their independence.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>During the evacuation, stop to answer students' questions to ensure information is fully communicated.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Don't designate a specific assembly point; allow students to move freely after the drill ends.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>After the drill concludes, skip the debriefing and proceed directly to the next class.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>You're preparing for a history lesson on ancient civilizations, but suddenly receive notice that due to a school equipment malfunction, the multimedia teaching resources you had planned to use are unavailable. This has disrupted your original plan, and class time is approaching quickly. What would you do in this situation?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Immediately adjust the plan and use the blackboard and oral instruction to cover the key points about ancient civilizations.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quickly find alternative teaching aids, such as wall charts or physical models, to substitute for the original materials.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Organize students into small groups for discussion, having them explore topics about ancient civilizations based on their existing knowledge.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Invite students to role-play characters from ancient civilizations through impromptu dramatization to deepen their understanding.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Utilize other available school equipment, such as a projector or audio player, to present relevant historical materials.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Postpone the class and wait for the equipment to be repaired before proceeding with the original teaching plan.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Simplify the lesson content and focus only on the most essential knowledge points about ancient civilizations.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Borrow usable multimedia teaching resources from other teachers to complete the lesson as planned.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Review previously learned related content with students as an introduction to the new lesson.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arrange for students to engage in self-study and provide printed materials for them to read and research.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cancel the class and have students do independent study or engage in other activities instead.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Insist on waiting for the multimedia equipment to be repaired without making any teaching adjustments.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Complain about the equipment failure and express dissatisfaction with the school's facilities.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Have students search for information about ancient civilizations on their own without providing guidance.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ignore the equipment malfunction and continue with the original plan regardless of the impact on students' learning experience.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>When grading exams, you discover that one question contains ambiguities, resulting in a wide variety of student answers. You realize this was an oversight when creating the test. What would you do in this situation?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Immediately organize a meeting with fellow teachers to discuss and establish unified grading criteria before regrading.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Promptly consult with the department head to develop a solution and provide an explanation to students.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thoroughly analyze the ambiguities of the question, develop comprehensive grading criteria, then re-grade all answers.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Include student representatives in the decision-making process to collaboratively determine the fairest grading criteria.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Issue a timely announcement acknowledging the error and outlining fair actions to address the situation.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Award partial score based on each student's past performance, while explaining your reasoning.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Make a notation about the ambiguity on the exam papers and address the issue in detail during the class.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Meet with students individually to understand their interpretation of the question then re-grade.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Allow the class to vote democratically on the preferred grading criteria based on majority opinion.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Temporarily defer grading this question while awaiting official guidance from school administration.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disregard the ambiguity and continue grading according to my own interpretation.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Award full score to all students for this question to resolve the issue quickly.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blame students for misinterpreting the question and maintain original grading criteria.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Postpone addressing the issue, hoping students' concerns will diminish over time.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Privately negotiate with students who are dissatisfied with this issue to minimize complaints.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>While grading assignments, you discover that one student's answers differ significantly from the standard answers, yet their problem-solving approach shows considerable creativity. You realize this student may have a unique way of thinking, but also needs guidance to better understand and apply the knowledge. What would you do in this situation?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Schedule a one-on-one discussion with the student to explore their problem-solving approach and uncover their thinking potential.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Encourage the student to share their thought and guide them to compare it with the standard answer.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Publicly praise the student's creative thinking in class while pointing out areas that need improvement.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Invite the student to explore multiple solution methods for similar problems together to broaden their thinking perspective.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Provide the student with additional reference materials to help deepen their understanding of the key concepts.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leave written comments acknowledging the student's creativity while pointing out shortcomings in the assignment.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proactively ask the student about their perspective on the problem after class and offer appropriate guidance.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Discuss the student's situation with other teachers to seek additional guidance strategies.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>In the assignment feedback, offer specific suggestions to help the student improve their thinking approach.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Encourage the student to independently research related knowledge to enhance their problem-solving abilities.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disregard the student's creative thinking and focus only on whether the assignment answers are correct or incorrect.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Provide no evaluation of the student's work and let them develop freely without feedback.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Publicly criticize the student's answer in class, dampening their enthusiasm.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Simply mark the errors without providing any further guidance or feedback.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Require the student to revise strictly according to the standard answer without considering the validity of their problem-solving approach.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>You've noticed that during group discussions, several students consistently remain very passive and rarely express any opinions. You're concerned that this lack of participation may affect their learning outcomes and teamwork skills. What would you do in this situation?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Communicate privately with these students to understand their concerns and provide support.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Design role-playing activities to encourage them to actively share their opinions.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adjust the group discussion format by implementing a turn-taking speaking mechanism.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Invite these students to prepare discussion materials in advance to build their confidence.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Provide positive feedback after discussions, emphasizing the value of participation.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Encourage other students within the group to actively invite them to speak.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set clear objectives for group discussions to enhance overall participation.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Provide additional reading materials to spark their interest in the topics.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Record the group discussion process for them to review and learn from.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Openly discuss the importance of participation in class.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ignore the situation, assuming they will gradually participate on their own.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Force every student to speak regardless of whether they are willing to do so.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Individually criticize these students for not participating in discussions.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Make no changes to the current group discussion approach.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assume this situation is only temporary and take no action.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>You receive a phone call from a parent reporting that their child has recently been bullied by classmates. You fully understand the severity of school bullying and are determined to take measures to protect the victim and prevent similar incidents from happening again. What would you do in this situation?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Immediately communicate with the victim to understand the specific situation and provide psychological support.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Organise a meeting with the students involved and their parents to discuss solutions together and ensure the issue is properly resolved.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Establish an anti-bullying policy for the school and strengthen educational outreach to students and staff.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Collaborate with the school administration to increase campus safety monitoring to prevent bullying incidents from recurring.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Regularly organize class activities to foster friendship and mutual trust among classmates, creating a harmonious atmosphere.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remind the victim to report bullying behavior to teachers or school authorities in a timely manner.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain the harmful effects of school bullying in class to raise students' awareness and prevention consciousness.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recommend that the school strengthen supervision of bullying to ensure timely detection and intervention.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Encourage students to monitor each other, promptly stop any bullying behavior they witness, and report it.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exchange experiences with other teachers to explore effective ways to address school bullying together.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Only give the students involved a verbal warning without taking any substantive measures.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disregard the parent's concern, dismissing it as just interaction between students.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wait for the bullying incident to resolve itself naturally without actively intervening.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Place all responsibility on the school, believing there's nothing you can do.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Express sympathy for the victim but take no action to help or protect them.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>You're organizing a campus cultural event but discover that the budget is far lower than you expected. You need to ensure the event's richness and quality within limited funding while also maintaining satisfaction among all participants. What would you do in this situation?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seek sponsorship from both on-campus and off-campus sources to increase funding.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consult with participants to adjust the event plan and reduce costs.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prioritize the core elements of the event and cut non-essential expenses.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Utilize existing school resources to minimize additional purchases.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Organize a volunteer team to reduce labor costs.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Streamline the event schedule to eliminate unnecessary expenditures.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Partner with cost-effective suppliers for better value.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use online platforms for promotion to attract more participants and share costs.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adjust the event timing appropriately to avoid peak periods and save on venue fees.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Encourage participants to bring some of their own supplies to reduce purchasing needs.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stick to the original plan without considering budget constraints.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arbitrarily cut event activities without considering the overall impact.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bear all expenses yourself without seeking any assistance.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disregard participants' opinions and make all event arrangements independently.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Purchase expensive items in pursuit of a luxurious effect.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>While teaching a new course, you discover that students are having difficulty understanding a certain abstract concept. You've tried explaining it in various ways, but the results are still unsatisfactory. You begin to think about how to use more intuitive and engaging methods to help students master this difficult point. What would you do in this situation?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use physical models for demonstration to help students intuitively grasp the concept.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Design interactive games that allow students to understand the abstract concept through gameplay.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Invite students who have already mastered the concept to share their understanding, promoting peer learning.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Create animated videos to assist with explanations and enhance visual impact.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Organize small group discussions to brainstorm and collectively tackle the difficult point.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assign related practice problems so students can deepen their understanding through hands-on application.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Provide additional reading materials to help students understand the concept from multiple perspectives.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adjust the teaching pace to give students more time to gradually absorb the new knowledge.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Provide one-on-one tutoring for struggling students, offering personalized guidance.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Encourage students to ask questions and address their specific doubts.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Repeat the previous explanation methods, hoping students will suddenly understand.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skip the difficult point and continue teaching subsequent content.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blame students for not working hard enough and apply pressure to force understanding.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ignore student feedback and insist on your own teaching methods.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rely solely on textbook explanations without attempting other teaching approaches.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>As a member of the school's teaching and research group, you've been asked to work with other teachers to develop a new teaching plan. You hope your ideas will be adopted, but you also know you need to reach consensus with other members. In this situation, how would you coordinate the relationship between your personal ideas and team collaboration?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prepare a detailed draft teaching plan in advance for everyone to discuss.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proactively communicate with other members to understand their thoughts and suggestions.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Actively speak up during discussions and support your viewpoints with data.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Showcase past successful teaching cases to enhance persuasiveness.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Invite senior teachers to participate in the discussion and leverage their influence.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Present your insights at appropriate times during discussions, avoiding being overly assertive.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Communicate privately with key members to gain their support.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Propose compromise solutions to facilitate consensus.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demonstrate the potential effectiveness of the new teaching plan to spark team interest.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Commit to taking on more responsibility during the implementation process.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Insist on your own views and refuse to make any compromises.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Frequently interrupt others while they're speaking during discussions.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Avoid discussing potential problems the new teaching plan might encounter.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disregard other members' opinions and only emphasize your own ideas.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Refuse to consider alternative plans proposed by other members.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>During class, you suddenly experience a power outage and the classroom becomes completely dark. Students begin to panic, and you know it will take some time to restore power. In this situation, how would you continue teaching while ensuring student safety and maintaining order?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Immediately calm students' emotions and use mobile phone flashlights to ensure safety.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quickly activate a backup teaching plan and conduct teaching activities that don't require electricity.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Organize students for small group discussions, using this opportunity for interactive learning.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use mobile phone hotspot to connect to the internet and switch to online teaching platforms.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guide students to use their phone lights for a creative "candlelight" classroom experience.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wait a moment, and after confirming power won't be restored immediately, make teaching adjustments.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Have students rest in place and resume normal teaching after power is restored.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ask students for suggestions and discuss coping strategies together.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Have students freely read textbooks or notes to maintain a learning state.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Borrow another classroom or venue to continue classroom teaching.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Be at a loss and let students handle the power outage situation on their own.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Insist on waiting for power restoration without making any teaching adjustments.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blame the school's inadequate facilities for disrupting normal teaching order.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ignore students' anxious emotions and continue trying to teach in the dark.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>End class early and let students leave the classroom on their own.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>You notice that a student frequently falls asleep in class, and their grades are suffering as a result. You suspect the student may be lacking sufficient sleep, which is detrimental to their physical and mental health as well as academic development. In this situation, how would you intervene and help the student improve this condition?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>You notice that a student frequently falls asleep in class, and their grades are suffering as a result. You suspect the student may be lacking sufficient sleep, which is detrimental to their physical and mental health as well as academic development. In this situation, how would you intervene and help the student?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Communicate privately with the student to understand the specific reasons for their sleep deprivation.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Contact the parents to jointly explore how to ensure the student gets adequate sleep.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adjust the classroom pace and insert interactive segments at appropriate times to increase student engagement.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Provide after-school tutoring to help the student make up for learning content missed due to lack of sleep.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest the school organize lectures on healthy sleep habits to raise student awareness.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remind the student in class to make them aware of the dozing problem.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adjust seating arrangements to place the student in a position where they're more easily noticed.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Encourage the student to take short breaks between classes to relieve fatigue.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Communicate with other subject teachers to collectively monitor the student's classroom condition.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remind the entire class about maintaining regular sleep schedules, indirectly influencing this student.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Publicly criticize the student and point out their dozing behavior.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ignore the student's problem, considering it just an isolated case.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Try to improve the student's attention by increasing homework load.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest the student solve the sleep problem on their own without providing specific help.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Directly recommend sleep medication to the student without understanding their situation first.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>You receive an anonymous letter from a student expressing dissatisfaction and complaints about a subject teacher. You realize this issue needs to be handled properly to maintain harmonious teacher-student relationships and stable teaching order. In this situation, how would you handle this anonymous letter?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Communicate privately with the subject teacher to understand the situation in detail and seek solutions.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Organize a class forum, inviting students to provide opinions and suggestions anonymously or openly.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Report to school management and jointly discuss the best way to handle this matter.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Encourage students to communicate directly with you or the subject teacher to enhance mutual understanding.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arrange teacher-student interactive activities to strengthen communication and trust.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Post an announcement in the class group reminding students to respect each teacher's teaching style.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Privately ask other students if they have similar feelings to gain a more comprehensive understanding of the situation.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest the student write a detailed feedback letter that you will forward to the subject teacher.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Invite a psychological counselor to intervene and help address the student's emotional issues.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Take no direct action for now and observe whether the situation improves.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ignore the letter, considering it just unreasonable complaints from an individual student.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Publicly criticize the student who wrote the letter as a warning to others.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Directly tell the subject teacher and let them handle the student's dissatisfaction themselves.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Require students to report with their real names, otherwise refuse to handle it.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disregard it, believing the problem will naturally disappear.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>You are preparing for an important open class, but suddenly receive notice that the originally scheduled classroom cannot be used due to maintenance. You need to quickly adjust your plan to ensure the open class proceeds smoothly while demonstrating your teaching ability and professional competence. In this situation, how would you respond to this unexpected circumstance?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Immediately contact the school for other available classrooms, rearrange and notify relevant personnel.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quickly check teaching materials to confirm they can be used smoothly in the new environment.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use the maintenance situation to design an on-site teaching case about dealing with unexpected situations.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Notify attending teachers and students, providing the new location and detailed directions.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adjust the teaching plan to ensure core content is not affected by the venue change.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consider postponing the open class and wait for the original classroom maintenance to be completed.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Do a trial run in the new classroom to ensure the teaching process flows smoothly.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Apply to the school for technical support to ensure the new classroom has complete equipment.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Simplify some teaching activities to adapt to the new environment.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cancel the open class and wait for the next opportunity.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Insist on using the original classroom without considering the maintenance situation.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Find and use a non-teaching space for the open class on your own.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Randomly choose a new classroom without any preparation work.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ignore the notice, assuming maintenance will be completed early.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ask if other teachers are willing to exchange classrooms.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>You notice that a student in your class is exceptionally gifted and performs outstandingly in a particular subject, far exceeding other classmates. You hope to fully develop this student's potential while preventing them from feeling isolated or overly pressured. In this situation, how would you balance this student's special needs with the overall teaching pace of the class?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arrange for the student to form a study group with peers who share similar interests to explore higher-level topics together.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Communicate privately with the student to understand their learning needs and provide personalized learning resources and guidance.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Establish a "subject assistant" role in the class, allowing the student to consolidate knowledge while helping others.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Encourage the student to participate in relevant subject competitions and provide appropriate preparation and support.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Conduct regular one-on-one feedback sessions with the student to ensure balance between learning progress and psychological well-being.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Publicly praise the student's achievements to inspire other classmates to learn from them.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arrange for the student to share learning experiences in class to promote communication among classmates.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recommend more challenging learning materials to the student to satisfy their thirst for knowledge.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Collaborate with other subject teachers to jointly focus on the student's comprehensive development.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Create a "study corner" in the classroom where the student has a dedicated space to discuss problems with classmates.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ignore the student's special performance and treat them the same as other students.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Frequently assign extra homework to the student alone, increasing their learning burden.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Over-emphasize the student's grades in class, causing tension in their relationships with other classmates.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disregard the student's interests and forcibly include them in tutoring groups for other subjects.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Make no intervention in the student's learning methods and achievements, letting them develop on their own.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1414,12 +2302,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1434,7 +2328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1456,24 +2350,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1959,7 +2842,8 @@
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="4" width="19.6640625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="56.33203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="44.6640625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="56.33203125" style="6" customWidth="1"/>
     <col min="7" max="15" width="9.1640625" customWidth="1"/>
     <col min="16" max="16" width="13" style="2" customWidth="1"/>
     <col min="17" max="17" width="13.5" style="3" customWidth="1"/>
@@ -1975,13 +2859,13 @@
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>341</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="11" t="s">
         <v>342</v>
       </c>
       <c r="G1" s="8" t="s">
@@ -3731,858 +4615,858 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="10" customFormat="1">
-      <c r="A32" s="10" t="s">
+    <row r="32" spans="1:18">
+      <c r="A32" t="s">
         <v>310</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="11" t="s">
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="F32" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="G32" s="13">
-        <v>3</v>
-      </c>
-      <c r="H32" s="13">
-        <v>1</v>
-      </c>
-      <c r="I32" s="13">
-        <v>3</v>
-      </c>
-      <c r="J32" s="13">
-        <v>2</v>
-      </c>
-      <c r="K32" s="13">
-        <v>1</v>
-      </c>
-      <c r="L32" s="13">
-        <v>7</v>
-      </c>
-      <c r="M32" s="13">
-        <v>4</v>
-      </c>
-      <c r="N32" s="13">
-        <v>3</v>
-      </c>
-      <c r="O32" s="13">
-        <v>1</v>
-      </c>
-      <c r="P32" s="14">
+      <c r="G32" s="5">
+        <v>3</v>
+      </c>
+      <c r="H32" s="5">
+        <v>1</v>
+      </c>
+      <c r="I32" s="5">
+        <v>3</v>
+      </c>
+      <c r="J32" s="5">
+        <v>2</v>
+      </c>
+      <c r="K32" s="5">
+        <v>1</v>
+      </c>
+      <c r="L32" s="5">
+        <v>7</v>
+      </c>
+      <c r="M32" s="5">
+        <v>4</v>
+      </c>
+      <c r="N32" s="5">
+        <v>3</v>
+      </c>
+      <c r="O32" s="5">
+        <v>1</v>
+      </c>
+      <c r="P32" s="2">
         <f t="shared" si="0"/>
         <v>2.7777777777777777</v>
       </c>
-      <c r="Q32" s="15">
-        <v>1</v>
-      </c>
-      <c r="R32" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" s="10" customFormat="1">
-      <c r="A33" s="10" t="s">
+      <c r="Q32" s="3">
+        <v>1</v>
+      </c>
+      <c r="R32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33" t="s">
         <v>310</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="11" t="s">
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="F33" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="G33" s="13">
-        <v>8</v>
-      </c>
-      <c r="H33" s="13">
-        <v>2</v>
-      </c>
-      <c r="I33" s="13">
-        <v>5</v>
-      </c>
-      <c r="J33" s="13">
-        <v>5</v>
-      </c>
-      <c r="K33" s="13">
-        <v>10</v>
-      </c>
-      <c r="L33" s="13">
-        <v>3</v>
-      </c>
-      <c r="M33" s="13">
-        <v>9</v>
-      </c>
-      <c r="N33" s="13">
-        <v>6</v>
-      </c>
-      <c r="O33" s="13">
-        <v>4</v>
-      </c>
-      <c r="P33" s="14">
+      <c r="G33" s="5">
+        <v>8</v>
+      </c>
+      <c r="H33" s="5">
+        <v>2</v>
+      </c>
+      <c r="I33" s="5">
+        <v>5</v>
+      </c>
+      <c r="J33" s="5">
+        <v>5</v>
+      </c>
+      <c r="K33" s="5">
+        <v>10</v>
+      </c>
+      <c r="L33" s="5">
+        <v>3</v>
+      </c>
+      <c r="M33" s="5">
+        <v>9</v>
+      </c>
+      <c r="N33" s="5">
+        <v>6</v>
+      </c>
+      <c r="O33" s="5">
+        <v>4</v>
+      </c>
+      <c r="P33" s="2">
         <f t="shared" si="0"/>
         <v>5.7777777777777777</v>
       </c>
-      <c r="Q33" s="16">
-        <v>6</v>
-      </c>
-      <c r="R33" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" s="10" customFormat="1">
-      <c r="A34" s="10" t="s">
+      <c r="Q33" s="9">
+        <v>6</v>
+      </c>
+      <c r="R33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34" t="s">
         <v>310</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" s="11" t="s">
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F34" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="G34" s="13">
-        <v>1</v>
-      </c>
-      <c r="H34" s="13">
-        <v>3</v>
-      </c>
-      <c r="I34" s="13">
-        <v>1</v>
-      </c>
-      <c r="J34" s="13">
-        <v>8</v>
-      </c>
-      <c r="K34" s="13">
-        <v>2</v>
-      </c>
-      <c r="L34" s="13">
-        <v>8</v>
-      </c>
-      <c r="M34" s="13">
-        <v>8</v>
-      </c>
-      <c r="N34" s="13">
-        <v>8</v>
-      </c>
-      <c r="O34" s="13">
-        <v>3</v>
-      </c>
-      <c r="P34" s="14">
+      <c r="G34" s="5">
+        <v>1</v>
+      </c>
+      <c r="H34" s="5">
+        <v>3</v>
+      </c>
+      <c r="I34" s="5">
+        <v>1</v>
+      </c>
+      <c r="J34" s="5">
+        <v>8</v>
+      </c>
+      <c r="K34" s="5">
+        <v>2</v>
+      </c>
+      <c r="L34" s="5">
+        <v>8</v>
+      </c>
+      <c r="M34" s="5">
+        <v>8</v>
+      </c>
+      <c r="N34" s="5">
+        <v>8</v>
+      </c>
+      <c r="O34" s="5">
+        <v>3</v>
+      </c>
+      <c r="P34" s="2">
         <f t="shared" si="0"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="Q34" s="15">
-        <v>3</v>
-      </c>
-      <c r="R34" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" s="10" customFormat="1">
-      <c r="A35" s="10" t="s">
+      <c r="Q34" s="3">
+        <v>3</v>
+      </c>
+      <c r="R34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35" t="s">
         <v>310</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="11" t="s">
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E35" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="F35" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="G35" s="13">
-        <v>7</v>
-      </c>
-      <c r="H35" s="13">
-        <v>4</v>
-      </c>
-      <c r="I35" s="13">
-        <v>10</v>
-      </c>
-      <c r="J35" s="13">
-        <v>12</v>
-      </c>
-      <c r="K35" s="13">
-        <v>5</v>
-      </c>
-      <c r="L35" s="13">
-        <v>6</v>
-      </c>
-      <c r="M35" s="13">
-        <v>2</v>
-      </c>
-      <c r="N35" s="13">
-        <v>9</v>
-      </c>
-      <c r="O35" s="13">
-        <v>5</v>
-      </c>
-      <c r="P35" s="14">
+      <c r="G35" s="5">
+        <v>7</v>
+      </c>
+      <c r="H35" s="5">
+        <v>4</v>
+      </c>
+      <c r="I35" s="5">
+        <v>10</v>
+      </c>
+      <c r="J35" s="5">
+        <v>12</v>
+      </c>
+      <c r="K35" s="5">
+        <v>5</v>
+      </c>
+      <c r="L35" s="5">
+        <v>6</v>
+      </c>
+      <c r="M35" s="5">
+        <v>2</v>
+      </c>
+      <c r="N35" s="5">
+        <v>9</v>
+      </c>
+      <c r="O35" s="5">
+        <v>5</v>
+      </c>
+      <c r="P35" s="2">
         <f t="shared" si="0"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="Q35" s="16">
-        <v>8</v>
-      </c>
-      <c r="R35" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" s="10" customFormat="1">
-      <c r="A36" s="10" t="s">
+      <c r="Q35" s="9">
+        <v>8</v>
+      </c>
+      <c r="R35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36" t="s">
         <v>310</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" s="11" t="s">
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F36" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="G36" s="13">
-        <v>2</v>
-      </c>
-      <c r="H36" s="13">
-        <v>5</v>
-      </c>
-      <c r="I36" s="13">
-        <v>7</v>
-      </c>
-      <c r="J36" s="13">
-        <v>1</v>
-      </c>
-      <c r="K36" s="13">
-        <v>3</v>
-      </c>
-      <c r="L36" s="13">
-        <v>1</v>
-      </c>
-      <c r="M36" s="13">
-        <v>5</v>
-      </c>
-      <c r="N36" s="13">
-        <v>1</v>
-      </c>
-      <c r="O36" s="13">
-        <v>2</v>
-      </c>
-      <c r="P36" s="14">
+      <c r="G36" s="5">
+        <v>2</v>
+      </c>
+      <c r="H36" s="5">
+        <v>5</v>
+      </c>
+      <c r="I36" s="5">
+        <v>7</v>
+      </c>
+      <c r="J36" s="5">
+        <v>1</v>
+      </c>
+      <c r="K36" s="5">
+        <v>3</v>
+      </c>
+      <c r="L36" s="5">
+        <v>1</v>
+      </c>
+      <c r="M36" s="5">
+        <v>5</v>
+      </c>
+      <c r="N36" s="5">
+        <v>1</v>
+      </c>
+      <c r="O36" s="5">
+        <v>2</v>
+      </c>
+      <c r="P36" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="Q36" s="15">
-        <v>2</v>
-      </c>
-      <c r="R36" s="10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" s="10" customFormat="1">
-      <c r="A37" s="10" t="s">
+      <c r="Q36" s="3">
+        <v>2</v>
+      </c>
+      <c r="R36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37" t="s">
         <v>310</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" s="11" t="s">
+      <c r="B37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F37" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="G37" s="13">
-        <v>9</v>
-      </c>
-      <c r="H37" s="13">
-        <v>6</v>
-      </c>
-      <c r="I37" s="13">
-        <v>4</v>
-      </c>
-      <c r="J37" s="13">
-        <v>3</v>
-      </c>
-      <c r="K37" s="13">
-        <v>4</v>
-      </c>
-      <c r="L37" s="13">
-        <v>2</v>
-      </c>
-      <c r="M37" s="13">
-        <v>6</v>
-      </c>
-      <c r="N37" s="13">
-        <v>7</v>
-      </c>
-      <c r="O37" s="13">
-        <v>6</v>
-      </c>
-      <c r="P37" s="14">
+      <c r="G37" s="5">
+        <v>9</v>
+      </c>
+      <c r="H37" s="5">
+        <v>6</v>
+      </c>
+      <c r="I37" s="5">
+        <v>4</v>
+      </c>
+      <c r="J37" s="5">
+        <v>3</v>
+      </c>
+      <c r="K37" s="5">
+        <v>4</v>
+      </c>
+      <c r="L37" s="5">
+        <v>2</v>
+      </c>
+      <c r="M37" s="5">
+        <v>6</v>
+      </c>
+      <c r="N37" s="5">
+        <v>7</v>
+      </c>
+      <c r="O37" s="5">
+        <v>6</v>
+      </c>
+      <c r="P37" s="2">
         <f t="shared" si="0"/>
         <v>5.2222222222222223</v>
       </c>
-      <c r="Q37" s="16">
-        <v>4</v>
-      </c>
-      <c r="R37" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" s="10" customFormat="1">
-      <c r="A38" s="10" t="s">
+      <c r="Q37" s="9">
+        <v>4</v>
+      </c>
+      <c r="R37">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
+      <c r="A38" t="s">
         <v>310</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="11" t="s">
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E38" s="12" t="s">
+      <c r="E38" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F38" s="12" t="s">
+      <c r="F38" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="G38" s="13">
-        <v>10</v>
-      </c>
-      <c r="H38" s="13">
-        <v>7</v>
-      </c>
-      <c r="I38" s="13">
-        <v>2</v>
-      </c>
-      <c r="J38" s="13">
-        <v>11</v>
-      </c>
-      <c r="K38" s="13">
-        <v>8</v>
-      </c>
-      <c r="L38" s="13">
-        <v>9</v>
-      </c>
-      <c r="M38" s="13">
-        <v>7</v>
-      </c>
-      <c r="N38" s="13">
-        <v>10</v>
-      </c>
-      <c r="O38" s="13">
-        <v>7</v>
-      </c>
-      <c r="P38" s="14">
+      <c r="G38" s="5">
+        <v>10</v>
+      </c>
+      <c r="H38" s="5">
+        <v>7</v>
+      </c>
+      <c r="I38" s="5">
+        <v>2</v>
+      </c>
+      <c r="J38" s="5">
+        <v>11</v>
+      </c>
+      <c r="K38" s="5">
+        <v>8</v>
+      </c>
+      <c r="L38" s="5">
+        <v>9</v>
+      </c>
+      <c r="M38" s="5">
+        <v>7</v>
+      </c>
+      <c r="N38" s="5">
+        <v>10</v>
+      </c>
+      <c r="O38" s="5">
+        <v>7</v>
+      </c>
+      <c r="P38" s="2">
         <f t="shared" si="0"/>
         <v>7.8888888888888893</v>
       </c>
-      <c r="Q38" s="15">
-        <v>10</v>
-      </c>
-      <c r="R38" s="10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" s="10" customFormat="1">
-      <c r="A39" s="10" t="s">
+      <c r="Q38" s="3">
+        <v>10</v>
+      </c>
+      <c r="R38">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
+      <c r="A39" t="s">
         <v>310</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D39" s="11" t="s">
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="E39" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F39" s="12" t="s">
+      <c r="F39" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="G39" s="13">
-        <v>4</v>
-      </c>
-      <c r="H39" s="13">
-        <v>8</v>
-      </c>
-      <c r="I39" s="13">
-        <v>8</v>
-      </c>
-      <c r="J39" s="13">
-        <v>6</v>
-      </c>
-      <c r="K39" s="13">
-        <v>9</v>
-      </c>
-      <c r="L39" s="13">
-        <v>10</v>
-      </c>
-      <c r="M39" s="13">
-        <v>3</v>
-      </c>
-      <c r="N39" s="13">
-        <v>2</v>
-      </c>
-      <c r="O39" s="13">
-        <v>9</v>
-      </c>
-      <c r="P39" s="14">
+      <c r="G39" s="5">
+        <v>4</v>
+      </c>
+      <c r="H39" s="5">
+        <v>8</v>
+      </c>
+      <c r="I39" s="5">
+        <v>8</v>
+      </c>
+      <c r="J39" s="5">
+        <v>6</v>
+      </c>
+      <c r="K39" s="5">
+        <v>9</v>
+      </c>
+      <c r="L39" s="5">
+        <v>10</v>
+      </c>
+      <c r="M39" s="5">
+        <v>3</v>
+      </c>
+      <c r="N39" s="5">
+        <v>2</v>
+      </c>
+      <c r="O39" s="5">
+        <v>9</v>
+      </c>
+      <c r="P39" s="2">
         <f t="shared" si="0"/>
         <v>6.5555555555555554</v>
       </c>
-      <c r="Q39" s="15">
-        <v>7</v>
-      </c>
-      <c r="R39" s="10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" s="10" customFormat="1">
-      <c r="A40" s="10" t="s">
+      <c r="Q39" s="3">
+        <v>7</v>
+      </c>
+      <c r="R39">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
+      <c r="A40" t="s">
         <v>310</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40" s="11" t="s">
+      <c r="B40" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E40" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F40" s="12" t="s">
+      <c r="F40" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="G40" s="13">
-        <v>5</v>
-      </c>
-      <c r="H40" s="13">
-        <v>9</v>
-      </c>
-      <c r="I40" s="13">
-        <v>9</v>
-      </c>
-      <c r="J40" s="13">
-        <v>4</v>
-      </c>
-      <c r="K40" s="13">
-        <v>6</v>
-      </c>
-      <c r="L40" s="13">
-        <v>4</v>
-      </c>
-      <c r="M40" s="13">
-        <v>1</v>
-      </c>
-      <c r="N40" s="13">
-        <v>4</v>
-      </c>
-      <c r="O40" s="13">
-        <v>8</v>
-      </c>
-      <c r="P40" s="14">
+      <c r="G40" s="5">
+        <v>5</v>
+      </c>
+      <c r="H40" s="5">
+        <v>9</v>
+      </c>
+      <c r="I40" s="5">
+        <v>9</v>
+      </c>
+      <c r="J40" s="5">
+        <v>4</v>
+      </c>
+      <c r="K40" s="5">
+        <v>6</v>
+      </c>
+      <c r="L40" s="5">
+        <v>4</v>
+      </c>
+      <c r="M40" s="5">
+        <v>1</v>
+      </c>
+      <c r="N40" s="5">
+        <v>4</v>
+      </c>
+      <c r="O40" s="5">
+        <v>8</v>
+      </c>
+      <c r="P40" s="2">
         <f t="shared" si="0"/>
         <v>5.5555555555555554</v>
       </c>
-      <c r="Q40" s="16">
-        <v>5</v>
-      </c>
-      <c r="R40" s="10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" s="10" customFormat="1">
-      <c r="A41" s="10" t="s">
+      <c r="Q40" s="9">
+        <v>5</v>
+      </c>
+      <c r="R40">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
+      <c r="A41" t="s">
         <v>310</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" s="11" t="s">
+      <c r="B41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E41" s="12" t="s">
+      <c r="E41" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F41" s="12" t="s">
+      <c r="F41" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="G41" s="13">
-        <v>6</v>
-      </c>
-      <c r="H41" s="13">
-        <v>10</v>
-      </c>
-      <c r="I41" s="13">
-        <v>6</v>
-      </c>
-      <c r="J41" s="13">
-        <v>7</v>
-      </c>
-      <c r="K41" s="13">
-        <v>7</v>
-      </c>
-      <c r="L41" s="13">
-        <v>5</v>
-      </c>
-      <c r="M41" s="13">
-        <v>10</v>
-      </c>
-      <c r="N41" s="13">
-        <v>5</v>
-      </c>
-      <c r="O41" s="13">
-        <v>10</v>
-      </c>
-      <c r="P41" s="14">
+      <c r="G41" s="5">
+        <v>6</v>
+      </c>
+      <c r="H41" s="5">
+        <v>10</v>
+      </c>
+      <c r="I41" s="5">
+        <v>6</v>
+      </c>
+      <c r="J41" s="5">
+        <v>7</v>
+      </c>
+      <c r="K41" s="5">
+        <v>7</v>
+      </c>
+      <c r="L41" s="5">
+        <v>5</v>
+      </c>
+      <c r="M41" s="5">
+        <v>10</v>
+      </c>
+      <c r="N41" s="5">
+        <v>5</v>
+      </c>
+      <c r="O41" s="5">
+        <v>10</v>
+      </c>
+      <c r="P41" s="2">
         <f t="shared" si="0"/>
         <v>7.333333333333333</v>
       </c>
-      <c r="Q41" s="15">
-        <v>9</v>
-      </c>
-      <c r="R41" s="10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" s="10" customFormat="1">
-      <c r="A42" s="10" t="s">
+      <c r="Q41" s="3">
+        <v>9</v>
+      </c>
+      <c r="R41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
+      <c r="A42" t="s">
         <v>310</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="11" t="s">
+      <c r="B42" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E42" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="F42" s="12" t="s">
+      <c r="F42" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="G42" s="13">
-        <v>11</v>
-      </c>
-      <c r="H42" s="13">
-        <v>15</v>
-      </c>
-      <c r="I42" s="13">
-        <v>14</v>
-      </c>
-      <c r="J42" s="13">
-        <v>14</v>
-      </c>
-      <c r="K42" s="13">
-        <v>13</v>
-      </c>
-      <c r="L42" s="13">
-        <v>13</v>
-      </c>
-      <c r="M42" s="13">
-        <v>14</v>
-      </c>
-      <c r="N42" s="13">
-        <v>11</v>
-      </c>
-      <c r="O42" s="13">
-        <v>15</v>
-      </c>
-      <c r="P42" s="14">
+      <c r="G42" s="5">
+        <v>11</v>
+      </c>
+      <c r="H42" s="5">
+        <v>15</v>
+      </c>
+      <c r="I42" s="5">
+        <v>14</v>
+      </c>
+      <c r="J42" s="5">
+        <v>14</v>
+      </c>
+      <c r="K42" s="5">
+        <v>13</v>
+      </c>
+      <c r="L42" s="5">
+        <v>13</v>
+      </c>
+      <c r="M42" s="5">
+        <v>14</v>
+      </c>
+      <c r="N42" s="5">
+        <v>11</v>
+      </c>
+      <c r="O42" s="5">
+        <v>15</v>
+      </c>
+      <c r="P42" s="2">
         <f t="shared" si="0"/>
         <v>13.333333333333334</v>
       </c>
-      <c r="Q42" s="15">
-        <v>14</v>
-      </c>
-      <c r="R42" s="10">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" s="10" customFormat="1">
-      <c r="A43" s="10" t="s">
+      <c r="Q42" s="3">
+        <v>14</v>
+      </c>
+      <c r="R42">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="A43" t="s">
         <v>310</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D43" s="11" t="s">
+      <c r="B43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="E43" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F43" s="12" t="s">
+      <c r="F43" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="G43" s="13">
-        <v>12</v>
-      </c>
-      <c r="H43" s="13">
-        <v>11</v>
-      </c>
-      <c r="I43" s="13">
-        <v>11</v>
-      </c>
-      <c r="J43" s="13">
-        <v>13</v>
-      </c>
-      <c r="K43" s="13">
-        <v>12</v>
-      </c>
-      <c r="L43" s="13">
-        <v>12</v>
-      </c>
-      <c r="M43" s="13">
-        <v>11</v>
-      </c>
-      <c r="N43" s="13">
-        <v>13</v>
-      </c>
-      <c r="O43" s="13">
-        <v>11</v>
-      </c>
-      <c r="P43" s="14">
+      <c r="G43" s="5">
+        <v>12</v>
+      </c>
+      <c r="H43" s="5">
+        <v>11</v>
+      </c>
+      <c r="I43" s="5">
+        <v>11</v>
+      </c>
+      <c r="J43" s="5">
+        <v>13</v>
+      </c>
+      <c r="K43" s="5">
+        <v>12</v>
+      </c>
+      <c r="L43" s="5">
+        <v>12</v>
+      </c>
+      <c r="M43" s="5">
+        <v>11</v>
+      </c>
+      <c r="N43" s="5">
+        <v>13</v>
+      </c>
+      <c r="O43" s="5">
+        <v>11</v>
+      </c>
+      <c r="P43" s="2">
         <f t="shared" si="0"/>
         <v>11.777777777777779</v>
       </c>
-      <c r="Q43" s="15">
-        <v>11</v>
-      </c>
-      <c r="R43" s="10">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" s="10" customFormat="1">
-      <c r="A44" s="10" t="s">
+      <c r="Q43" s="3">
+        <v>11</v>
+      </c>
+      <c r="R43">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
+      <c r="A44" t="s">
         <v>310</v>
       </c>
-      <c r="B44" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44" s="11" t="s">
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F44" s="12" t="s">
+      <c r="F44" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="G44" s="13">
-        <v>13</v>
-      </c>
-      <c r="H44" s="13">
-        <v>12</v>
-      </c>
-      <c r="I44" s="13">
-        <v>12</v>
-      </c>
-      <c r="J44" s="13">
-        <v>9</v>
-      </c>
-      <c r="K44" s="13">
-        <v>11</v>
-      </c>
-      <c r="L44" s="13">
-        <v>14</v>
-      </c>
-      <c r="M44" s="13">
-        <v>12</v>
-      </c>
-      <c r="N44" s="13">
-        <v>12</v>
-      </c>
-      <c r="O44" s="13">
-        <v>12</v>
-      </c>
-      <c r="P44" s="14">
+      <c r="G44" s="5">
+        <v>13</v>
+      </c>
+      <c r="H44" s="5">
+        <v>12</v>
+      </c>
+      <c r="I44" s="5">
+        <v>12</v>
+      </c>
+      <c r="J44" s="5">
+        <v>9</v>
+      </c>
+      <c r="K44" s="5">
+        <v>11</v>
+      </c>
+      <c r="L44" s="5">
+        <v>14</v>
+      </c>
+      <c r="M44" s="5">
+        <v>12</v>
+      </c>
+      <c r="N44" s="5">
+        <v>12</v>
+      </c>
+      <c r="O44" s="5">
+        <v>12</v>
+      </c>
+      <c r="P44" s="2">
         <f t="shared" si="0"/>
         <v>11.888888888888889</v>
       </c>
-      <c r="Q44" s="15">
-        <v>12</v>
-      </c>
-      <c r="R44" s="10">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" s="10" customFormat="1">
-      <c r="A45" s="10" t="s">
+      <c r="Q44" s="3">
+        <v>12</v>
+      </c>
+      <c r="R44">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
+      <c r="A45" t="s">
         <v>310</v>
       </c>
-      <c r="B45" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D45" s="11" t="s">
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E45" s="12" t="s">
+      <c r="E45" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F45" s="12" t="s">
+      <c r="F45" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="G45" s="13">
-        <v>14</v>
-      </c>
-      <c r="H45" s="13">
-        <v>13</v>
-      </c>
-      <c r="I45" s="13">
-        <v>13</v>
-      </c>
-      <c r="J45" s="13">
-        <v>10</v>
-      </c>
-      <c r="K45" s="13">
-        <v>14</v>
-      </c>
-      <c r="L45" s="13">
-        <v>11</v>
-      </c>
-      <c r="M45" s="13">
-        <v>13</v>
-      </c>
-      <c r="N45" s="13">
-        <v>14</v>
-      </c>
-      <c r="O45" s="13">
-        <v>13</v>
-      </c>
-      <c r="P45" s="14">
+      <c r="G45" s="5">
+        <v>14</v>
+      </c>
+      <c r="H45" s="5">
+        <v>13</v>
+      </c>
+      <c r="I45" s="5">
+        <v>13</v>
+      </c>
+      <c r="J45" s="5">
+        <v>10</v>
+      </c>
+      <c r="K45" s="5">
+        <v>14</v>
+      </c>
+      <c r="L45" s="5">
+        <v>11</v>
+      </c>
+      <c r="M45" s="5">
+        <v>13</v>
+      </c>
+      <c r="N45" s="5">
+        <v>14</v>
+      </c>
+      <c r="O45" s="5">
+        <v>13</v>
+      </c>
+      <c r="P45" s="2">
         <f t="shared" si="0"/>
         <v>12.777777777777779</v>
       </c>
-      <c r="Q45" s="15">
-        <v>13</v>
-      </c>
-      <c r="R45" s="10">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" s="10" customFormat="1">
-      <c r="A46" s="10" t="s">
+      <c r="Q45" s="3">
+        <v>13</v>
+      </c>
+      <c r="R45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
+      <c r="A46" t="s">
         <v>310</v>
       </c>
-      <c r="B46" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" s="11" t="s">
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E46" s="12" t="s">
+      <c r="E46" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F46" s="12" t="s">
+      <c r="F46" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="G46" s="13">
-        <v>15</v>
-      </c>
-      <c r="H46" s="13">
-        <v>14</v>
-      </c>
-      <c r="I46" s="13">
-        <v>15</v>
-      </c>
-      <c r="J46" s="13">
-        <v>15</v>
-      </c>
-      <c r="K46" s="13">
-        <v>15</v>
-      </c>
-      <c r="L46" s="13">
-        <v>15</v>
-      </c>
-      <c r="M46" s="13">
-        <v>15</v>
-      </c>
-      <c r="N46" s="13">
-        <v>15</v>
-      </c>
-      <c r="O46" s="13">
-        <v>14</v>
-      </c>
-      <c r="P46" s="14">
+      <c r="G46" s="5">
+        <v>15</v>
+      </c>
+      <c r="H46" s="5">
+        <v>14</v>
+      </c>
+      <c r="I46" s="5">
+        <v>15</v>
+      </c>
+      <c r="J46" s="5">
+        <v>15</v>
+      </c>
+      <c r="K46" s="5">
+        <v>15</v>
+      </c>
+      <c r="L46" s="5">
+        <v>15</v>
+      </c>
+      <c r="M46" s="5">
+        <v>15</v>
+      </c>
+      <c r="N46" s="5">
+        <v>15</v>
+      </c>
+      <c r="O46" s="5">
+        <v>14</v>
+      </c>
+      <c r="P46" s="2">
         <f t="shared" si="0"/>
         <v>14.777777777777779</v>
       </c>
-      <c r="Q46" s="15">
-        <v>15</v>
-      </c>
-      <c r="R46" s="10">
+      <c r="Q46" s="3">
+        <v>15</v>
+      </c>
+      <c r="R46">
         <v>15</v>
       </c>
     </row>
@@ -5449,16 +6333,16 @@
         <v>14</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>15</v>
+        <v>409</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>100</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G62" s="5">
         <v>5</v>
@@ -5509,13 +6393,13 @@
         <v>15</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>101</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G63" s="5">
         <v>1</v>
@@ -5566,13 +6450,13 @@
         <v>15</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>102</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G64" s="5">
         <v>2</v>
@@ -5623,12 +6507,14 @@
         <v>15</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F65" s="7"/>
+      <c r="F65" s="7" t="s">
+        <v>411</v>
+      </c>
       <c r="G65" s="5">
         <v>3</v>
       </c>
@@ -5678,12 +6564,14 @@
         <v>15</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="F66" s="7"/>
+      <c r="F66" s="7" t="s">
+        <v>412</v>
+      </c>
       <c r="G66" s="5">
         <v>9</v>
       </c>
@@ -5733,12 +6621,14 @@
         <v>15</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="F67" s="7"/>
+      <c r="F67" s="7" t="s">
+        <v>413</v>
+      </c>
       <c r="G67" s="5">
         <v>4</v>
       </c>
@@ -5788,12 +6678,14 @@
         <v>15</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F68" s="7"/>
+      <c r="F68" s="7" t="s">
+        <v>414</v>
+      </c>
       <c r="G68" s="5">
         <v>6</v>
       </c>
@@ -5843,12 +6735,14 @@
         <v>15</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="F69" s="7"/>
+      <c r="F69" s="7" t="s">
+        <v>415</v>
+      </c>
       <c r="G69" s="5">
         <v>7</v>
       </c>
@@ -5898,12 +6792,14 @@
         <v>15</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F70" s="7"/>
+      <c r="F70" s="7" t="s">
+        <v>416</v>
+      </c>
       <c r="G70" s="5">
         <v>8</v>
       </c>
@@ -5953,12 +6849,14 @@
         <v>15</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F71" s="7"/>
+      <c r="F71" s="7" t="s">
+        <v>417</v>
+      </c>
       <c r="G71" s="5">
         <v>10</v>
       </c>
@@ -6008,12 +6906,14 @@
         <v>15</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F72" s="7"/>
+      <c r="F72" s="7" t="s">
+        <v>418</v>
+      </c>
       <c r="G72" s="5">
         <v>11</v>
       </c>
@@ -6063,12 +6963,14 @@
         <v>15</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="F73" s="7"/>
+      <c r="F73" s="7" t="s">
+        <v>419</v>
+      </c>
       <c r="G73" s="5">
         <v>12</v>
       </c>
@@ -6118,12 +7020,14 @@
         <v>15</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="F74" s="7"/>
+      <c r="F74" s="7" t="s">
+        <v>420</v>
+      </c>
       <c r="G74" s="5">
         <v>13</v>
       </c>
@@ -6173,12 +7077,14 @@
         <v>15</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="F75" s="7"/>
+      <c r="F75" s="7" t="s">
+        <v>421</v>
+      </c>
       <c r="G75" s="5">
         <v>14</v>
       </c>
@@ -6228,12 +7134,14 @@
         <v>15</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="F76" s="7"/>
+      <c r="F76" s="7" t="s">
+        <v>422</v>
+      </c>
       <c r="G76" s="5">
         <v>15</v>
       </c>
@@ -6282,11 +7190,15 @@
       <c r="C77" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D77" s="4"/>
+      <c r="D77" s="4" t="s">
+        <v>423</v>
+      </c>
       <c r="E77" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="F77" s="7"/>
+      <c r="F77" s="7" t="s">
+        <v>424</v>
+      </c>
       <c r="G77" s="5">
         <v>7</v>
       </c>
@@ -6335,11 +7247,15 @@
       <c r="C78" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="4"/>
+      <c r="D78" s="4" t="s">
+        <v>423</v>
+      </c>
       <c r="E78" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="F78" s="7"/>
+      <c r="F78" s="7" t="s">
+        <v>425</v>
+      </c>
       <c r="G78" s="5">
         <v>1</v>
       </c>
@@ -6388,11 +7304,15 @@
       <c r="C79" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D79" s="4"/>
+      <c r="D79" s="4" t="s">
+        <v>423</v>
+      </c>
       <c r="E79" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="F79" s="7"/>
+      <c r="F79" s="7" t="s">
+        <v>426</v>
+      </c>
       <c r="G79" s="5">
         <v>4</v>
       </c>
@@ -6441,11 +7361,15 @@
       <c r="C80" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D80" s="4"/>
+      <c r="D80" s="4" t="s">
+        <v>423</v>
+      </c>
       <c r="E80" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="F80" s="7"/>
+      <c r="F80" s="7" t="s">
+        <v>427</v>
+      </c>
       <c r="G80" s="5">
         <v>2</v>
       </c>
@@ -6494,11 +7418,15 @@
       <c r="C81" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D81" s="4"/>
+      <c r="D81" s="4" t="s">
+        <v>423</v>
+      </c>
       <c r="E81" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="F81" s="7"/>
+      <c r="F81" s="7" t="s">
+        <v>428</v>
+      </c>
       <c r="G81" s="5">
         <v>3</v>
       </c>
@@ -6547,11 +7475,15 @@
       <c r="C82" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D82" s="4"/>
+      <c r="D82" s="4" t="s">
+        <v>423</v>
+      </c>
       <c r="E82" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="F82" s="7"/>
+      <c r="F82" s="7" t="s">
+        <v>429</v>
+      </c>
       <c r="G82" s="5">
         <v>11</v>
       </c>
@@ -6600,11 +7532,15 @@
       <c r="C83" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D83" s="4"/>
+      <c r="D83" s="4" t="s">
+        <v>423</v>
+      </c>
       <c r="E83" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="F83" s="7"/>
+      <c r="F83" s="7" t="s">
+        <v>430</v>
+      </c>
       <c r="G83" s="5">
         <v>8</v>
       </c>
@@ -6653,11 +7589,15 @@
       <c r="C84" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D84" s="4"/>
+      <c r="D84" s="4" t="s">
+        <v>423</v>
+      </c>
       <c r="E84" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="F84" s="7"/>
+      <c r="F84" s="7" t="s">
+        <v>431</v>
+      </c>
       <c r="G84" s="5">
         <v>5</v>
       </c>
@@ -6706,11 +7646,15 @@
       <c r="C85" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D85" s="4"/>
+      <c r="D85" s="4" t="s">
+        <v>423</v>
+      </c>
       <c r="E85" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F85" s="7"/>
+      <c r="F85" s="7" t="s">
+        <v>432</v>
+      </c>
       <c r="G85" s="5">
         <v>6</v>
       </c>
@@ -6759,11 +7703,15 @@
       <c r="C86" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D86" s="4"/>
+      <c r="D86" s="4" t="s">
+        <v>423</v>
+      </c>
       <c r="E86" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="F86" s="7"/>
+      <c r="F86" s="7" t="s">
+        <v>433</v>
+      </c>
       <c r="G86" s="5">
         <v>9</v>
       </c>
@@ -6812,11 +7760,15 @@
       <c r="C87" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D87" s="4"/>
+      <c r="D87" s="4" t="s">
+        <v>423</v>
+      </c>
       <c r="E87" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="F87" s="7"/>
+      <c r="F87" s="7" t="s">
+        <v>434</v>
+      </c>
       <c r="G87" s="5">
         <v>10</v>
       </c>
@@ -6865,11 +7817,15 @@
       <c r="C88" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D88" s="4"/>
+      <c r="D88" s="4" t="s">
+        <v>423</v>
+      </c>
       <c r="E88" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="F88" s="7"/>
+      <c r="F88" s="7" t="s">
+        <v>435</v>
+      </c>
       <c r="G88" s="5">
         <v>12</v>
       </c>
@@ -6918,11 +7874,15 @@
       <c r="C89" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D89" s="4"/>
+      <c r="D89" s="4" t="s">
+        <v>423</v>
+      </c>
       <c r="E89" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="F89" s="7"/>
+      <c r="F89" s="7" t="s">
+        <v>436</v>
+      </c>
       <c r="G89" s="5">
         <v>13</v>
       </c>
@@ -6971,11 +7931,15 @@
       <c r="C90" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D90" s="4"/>
+      <c r="D90" s="4" t="s">
+        <v>423</v>
+      </c>
       <c r="E90" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="F90" s="7"/>
+      <c r="F90" s="7" t="s">
+        <v>437</v>
+      </c>
       <c r="G90" s="5">
         <v>14</v>
       </c>
@@ -7024,11 +7988,15 @@
       <c r="C91" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D91" s="4"/>
+      <c r="D91" s="4" t="s">
+        <v>423</v>
+      </c>
       <c r="E91" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="F91" s="7"/>
+      <c r="F91" s="7" t="s">
+        <v>438</v>
+      </c>
       <c r="G91" s="5">
         <v>15</v>
       </c>
@@ -7077,11 +8045,15 @@
       <c r="C92" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D92" s="4"/>
+      <c r="D92" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="E92" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="F92" s="7"/>
+      <c r="F92" s="7" t="s">
+        <v>456</v>
+      </c>
       <c r="G92" s="5">
         <v>7</v>
       </c>
@@ -7130,11 +8102,15 @@
       <c r="C93" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D93" s="4"/>
+      <c r="D93" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="E93" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="F93" s="7"/>
+      <c r="F93" s="7" t="s">
+        <v>457</v>
+      </c>
       <c r="G93" s="5">
         <v>9</v>
       </c>
@@ -7183,11 +8159,15 @@
       <c r="C94" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D94" s="4"/>
+      <c r="D94" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="E94" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="F94" s="7"/>
+      <c r="F94" s="7" t="s">
+        <v>458</v>
+      </c>
       <c r="G94" s="5">
         <v>1</v>
       </c>
@@ -7236,11 +8216,15 @@
       <c r="C95" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D95" s="4"/>
+      <c r="D95" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="E95" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="F95" s="7"/>
+      <c r="F95" s="7" t="s">
+        <v>459</v>
+      </c>
       <c r="G95" s="5">
         <v>2</v>
       </c>
@@ -7289,11 +8273,15 @@
       <c r="C96" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D96" s="4"/>
+      <c r="D96" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="E96" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="F96" s="7"/>
+      <c r="F96" s="7" t="s">
+        <v>460</v>
+      </c>
       <c r="G96" s="5">
         <v>3</v>
       </c>
@@ -7342,11 +8330,15 @@
       <c r="C97" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D97" s="4"/>
+      <c r="D97" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="E97" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="F97" s="7"/>
+      <c r="F97" s="7" t="s">
+        <v>461</v>
+      </c>
       <c r="G97" s="5">
         <v>4</v>
       </c>
@@ -7395,11 +8387,15 @@
       <c r="C98" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D98" s="4"/>
+      <c r="D98" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="E98" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="F98" s="7"/>
+      <c r="F98" s="7" t="s">
+        <v>462</v>
+      </c>
       <c r="G98" s="5">
         <v>5</v>
       </c>
@@ -7448,11 +8444,15 @@
       <c r="C99" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D99" s="4"/>
+      <c r="D99" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="E99" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F99" s="7"/>
+      <c r="F99" s="7" t="s">
+        <v>463</v>
+      </c>
       <c r="G99" s="5">
         <v>6</v>
       </c>
@@ -7501,11 +8501,15 @@
       <c r="C100" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D100" s="4"/>
+      <c r="D100" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="E100" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="F100" s="7"/>
+      <c r="F100" s="7" t="s">
+        <v>464</v>
+      </c>
       <c r="G100" s="5">
         <v>10</v>
       </c>
@@ -7554,11 +8558,15 @@
       <c r="C101" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D101" s="4"/>
+      <c r="D101" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="E101" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="F101" s="7"/>
+      <c r="F101" s="7" t="s">
+        <v>465</v>
+      </c>
       <c r="G101" s="5">
         <v>8</v>
       </c>
@@ -7607,11 +8615,15 @@
       <c r="C102" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D102" s="4"/>
+      <c r="D102" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="E102" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="F102" s="7"/>
+      <c r="F102" s="7" t="s">
+        <v>466</v>
+      </c>
       <c r="G102" s="5">
         <v>11</v>
       </c>
@@ -7660,11 +8672,15 @@
       <c r="C103" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D103" s="4"/>
+      <c r="D103" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="E103" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="F103" s="7"/>
+      <c r="F103" s="7" t="s">
+        <v>467</v>
+      </c>
       <c r="G103" s="5">
         <v>12</v>
       </c>
@@ -7713,11 +8729,15 @@
       <c r="C104" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D104" s="4"/>
+      <c r="D104" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="E104" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="F104" s="7"/>
+      <c r="F104" s="7" t="s">
+        <v>468</v>
+      </c>
       <c r="G104" s="5">
         <v>13</v>
       </c>
@@ -7766,11 +8786,15 @@
       <c r="C105" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D105" s="4"/>
+      <c r="D105" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="E105" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="F105" s="7"/>
+      <c r="F105" s="7" t="s">
+        <v>469</v>
+      </c>
       <c r="G105" s="5">
         <v>14</v>
       </c>
@@ -7819,11 +8843,15 @@
       <c r="C106" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D106" s="4"/>
+      <c r="D106" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="E106" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="F106" s="7"/>
+      <c r="F106" s="7" t="s">
+        <v>470</v>
+      </c>
       <c r="G106" s="5">
         <v>15</v>
       </c>
@@ -7872,11 +8900,15 @@
       <c r="C107" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D107" s="4"/>
+      <c r="D107" s="4" t="s">
+        <v>471</v>
+      </c>
       <c r="E107" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F107" s="7"/>
+      <c r="F107" s="7" t="s">
+        <v>472</v>
+      </c>
       <c r="G107" s="5">
         <v>8</v>
       </c>
@@ -7929,7 +8961,9 @@
       <c r="E108" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="F108" s="7"/>
+      <c r="F108" s="7" t="s">
+        <v>473</v>
+      </c>
       <c r="G108" s="5">
         <v>4</v>
       </c>
@@ -7982,7 +9016,9 @@
       <c r="E109" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="F109" s="7"/>
+      <c r="F109" s="7" t="s">
+        <v>474</v>
+      </c>
       <c r="G109" s="5">
         <v>5</v>
       </c>
@@ -8035,7 +9071,9 @@
       <c r="E110" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="F110" s="7"/>
+      <c r="F110" s="7" t="s">
+        <v>475</v>
+      </c>
       <c r="G110" s="5">
         <v>1</v>
       </c>
@@ -8088,7 +9126,9 @@
       <c r="E111" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F111" s="7"/>
+      <c r="F111" s="7" t="s">
+        <v>476</v>
+      </c>
       <c r="G111" s="5">
         <v>6</v>
       </c>
@@ -8141,7 +9181,9 @@
       <c r="E112" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="F112" s="7"/>
+      <c r="F112" s="7" t="s">
+        <v>477</v>
+      </c>
       <c r="G112" s="5">
         <v>2</v>
       </c>
@@ -8194,7 +9236,9 @@
       <c r="E113" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F113" s="7"/>
+      <c r="F113" s="7" t="s">
+        <v>478</v>
+      </c>
       <c r="G113" s="5">
         <v>3</v>
       </c>
@@ -8247,7 +9291,9 @@
       <c r="E114" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F114" s="7"/>
+      <c r="F114" s="7" t="s">
+        <v>479</v>
+      </c>
       <c r="G114" s="5">
         <v>9</v>
       </c>
@@ -8300,7 +9346,9 @@
       <c r="E115" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="F115" s="7"/>
+      <c r="F115" s="7" t="s">
+        <v>480</v>
+      </c>
       <c r="G115" s="5">
         <v>10</v>
       </c>
@@ -8353,7 +9401,9 @@
       <c r="E116" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F116" s="7"/>
+      <c r="F116" s="7" t="s">
+        <v>481</v>
+      </c>
       <c r="G116" s="5">
         <v>7</v>
       </c>
@@ -8406,7 +9456,9 @@
       <c r="E117" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="F117" s="7"/>
+      <c r="F117" s="7" t="s">
+        <v>482</v>
+      </c>
       <c r="G117" s="5">
         <v>11</v>
       </c>
@@ -8459,7 +9511,9 @@
       <c r="E118" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="F118" s="7"/>
+      <c r="F118" s="7" t="s">
+        <v>483</v>
+      </c>
       <c r="G118" s="5">
         <v>12</v>
       </c>
@@ -8512,7 +9566,9 @@
       <c r="E119" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="F119" s="7"/>
+      <c r="F119" s="7" t="s">
+        <v>484</v>
+      </c>
       <c r="G119" s="5">
         <v>13</v>
       </c>
@@ -8565,7 +9621,9 @@
       <c r="E120" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="F120" s="7"/>
+      <c r="F120" s="7" t="s">
+        <v>485</v>
+      </c>
       <c r="G120" s="5">
         <v>14</v>
       </c>
@@ -8618,7 +9676,9 @@
       <c r="E121" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="F121" s="7"/>
+      <c r="F121" s="7" t="s">
+        <v>486</v>
+      </c>
       <c r="G121" s="5">
         <v>15</v>
       </c>
@@ -8667,11 +9727,15 @@
       <c r="C122" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D122" s="4"/>
+      <c r="D122" s="4" t="s">
+        <v>487</v>
+      </c>
       <c r="E122" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="F122" s="7"/>
+      <c r="F122" s="7" t="s">
+        <v>488</v>
+      </c>
       <c r="G122" s="5">
         <v>2</v>
       </c>
@@ -8724,7 +9788,9 @@
       <c r="E123" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="F123" s="7"/>
+      <c r="F123" s="7" t="s">
+        <v>489</v>
+      </c>
       <c r="G123" s="5">
         <v>4</v>
       </c>
@@ -8777,7 +9843,9 @@
       <c r="E124" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="F124" s="7"/>
+      <c r="F124" s="7" t="s">
+        <v>490</v>
+      </c>
       <c r="G124" s="5">
         <v>3</v>
       </c>
@@ -8830,7 +9898,9 @@
       <c r="E125" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F125" s="7"/>
+      <c r="F125" s="7" t="s">
+        <v>491</v>
+      </c>
       <c r="G125" s="5">
         <v>1</v>
       </c>
@@ -8883,7 +9953,9 @@
       <c r="E126" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F126" s="7"/>
+      <c r="F126" s="7" t="s">
+        <v>492</v>
+      </c>
       <c r="G126" s="5">
         <v>5</v>
       </c>
@@ -8936,7 +10008,9 @@
       <c r="E127" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F127" s="7"/>
+      <c r="F127" s="7" t="s">
+        <v>493</v>
+      </c>
       <c r="G127" s="5">
         <v>6</v>
       </c>
@@ -8989,7 +10063,9 @@
       <c r="E128" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="F128" s="7"/>
+      <c r="F128" s="7" t="s">
+        <v>494</v>
+      </c>
       <c r="G128" s="5">
         <v>10</v>
       </c>
@@ -9042,7 +10118,9 @@
       <c r="E129" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="F129" s="7"/>
+      <c r="F129" s="7" t="s">
+        <v>495</v>
+      </c>
       <c r="G129" s="5">
         <v>7</v>
       </c>
@@ -9095,7 +10173,9 @@
       <c r="E130" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="F130" s="7"/>
+      <c r="F130" s="7" t="s">
+        <v>496</v>
+      </c>
       <c r="G130" s="5">
         <v>8</v>
       </c>
@@ -9148,7 +10228,9 @@
       <c r="E131" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="F131" s="7"/>
+      <c r="F131" s="7" t="s">
+        <v>497</v>
+      </c>
       <c r="G131" s="5">
         <v>9</v>
       </c>
@@ -9201,7 +10283,9 @@
       <c r="E132" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="F132" s="7"/>
+      <c r="F132" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="G132" s="5">
         <v>11</v>
       </c>
@@ -9254,7 +10338,9 @@
       <c r="E133" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="F133" s="7"/>
+      <c r="F133" s="7" t="s">
+        <v>498</v>
+      </c>
       <c r="G133" s="5">
         <v>12</v>
       </c>
@@ -9307,7 +10393,9 @@
       <c r="E134" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="F134" s="7"/>
+      <c r="F134" s="7" t="s">
+        <v>500</v>
+      </c>
       <c r="G134" s="5">
         <v>13</v>
       </c>
@@ -9360,7 +10448,9 @@
       <c r="E135" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="F135" s="7"/>
+      <c r="F135" s="7" t="s">
+        <v>501</v>
+      </c>
       <c r="G135" s="5">
         <v>14</v>
       </c>
@@ -9413,7 +10503,9 @@
       <c r="E136" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="F136" s="7"/>
+      <c r="F136" s="7" t="s">
+        <v>502</v>
+      </c>
       <c r="G136" s="5">
         <v>15</v>
       </c>
@@ -9462,11 +10554,15 @@
       <c r="C137" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D137" s="4"/>
+      <c r="D137" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="E137" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="F137" s="7"/>
+      <c r="F137" s="7" t="s">
+        <v>504</v>
+      </c>
       <c r="G137" s="5">
         <v>10</v>
       </c>
@@ -9515,11 +10611,15 @@
       <c r="C138" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D138" s="4"/>
+      <c r="D138" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="E138" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="F138" s="7"/>
+      <c r="F138" s="7" t="s">
+        <v>505</v>
+      </c>
       <c r="G138" s="5">
         <v>1</v>
       </c>
@@ -9568,11 +10668,15 @@
       <c r="C139" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D139" s="4"/>
+      <c r="D139" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="E139" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="F139" s="7"/>
+      <c r="F139" s="7" t="s">
+        <v>506</v>
+      </c>
       <c r="G139" s="5">
         <v>2</v>
       </c>
@@ -9621,11 +10725,15 @@
       <c r="C140" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D140" s="4"/>
+      <c r="D140" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="E140" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="F140" s="7"/>
+      <c r="F140" s="7" t="s">
+        <v>507</v>
+      </c>
       <c r="G140" s="5">
         <v>3</v>
       </c>
@@ -9674,11 +10782,15 @@
       <c r="C141" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D141" s="4"/>
+      <c r="D141" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="E141" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="F141" s="7"/>
+      <c r="F141" s="7" t="s">
+        <v>508</v>
+      </c>
       <c r="G141" s="5">
         <v>4</v>
       </c>
@@ -9727,11 +10839,15 @@
       <c r="C142" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D142" s="4"/>
+      <c r="D142" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="E142" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="F142" s="7"/>
+      <c r="F142" s="7" t="s">
+        <v>509</v>
+      </c>
       <c r="G142" s="5">
         <v>5</v>
       </c>
@@ -9780,11 +10896,15 @@
       <c r="C143" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D143" s="4"/>
+      <c r="D143" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="E143" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="F143" s="7"/>
+      <c r="F143" s="7" t="s">
+        <v>510</v>
+      </c>
       <c r="G143" s="5">
         <v>6</v>
       </c>
@@ -9833,11 +10953,15 @@
       <c r="C144" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D144" s="4"/>
+      <c r="D144" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="E144" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="F144" s="7"/>
+      <c r="F144" s="7" t="s">
+        <v>511</v>
+      </c>
       <c r="G144" s="5">
         <v>7</v>
       </c>
@@ -9886,11 +11010,15 @@
       <c r="C145" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D145" s="4"/>
+      <c r="D145" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="E145" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="F145" s="7"/>
+      <c r="F145" s="7" t="s">
+        <v>512</v>
+      </c>
       <c r="G145" s="5">
         <v>8</v>
       </c>
@@ -9939,11 +11067,15 @@
       <c r="C146" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D146" s="4"/>
+      <c r="D146" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="E146" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="F146" s="7"/>
+      <c r="F146" s="7" t="s">
+        <v>513</v>
+      </c>
       <c r="G146" s="5">
         <v>9</v>
       </c>
@@ -9992,11 +11124,15 @@
       <c r="C147" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D147" s="4"/>
+      <c r="D147" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="E147" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="F147" s="7"/>
+      <c r="F147" s="7" t="s">
+        <v>514</v>
+      </c>
       <c r="G147" s="5">
         <v>12</v>
       </c>
@@ -10045,11 +11181,15 @@
       <c r="C148" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D148" s="4"/>
+      <c r="D148" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="E148" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="F148" s="7"/>
+      <c r="F148" s="7" t="s">
+        <v>515</v>
+      </c>
       <c r="G148" s="5">
         <v>11</v>
       </c>
@@ -10098,11 +11238,15 @@
       <c r="C149" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D149" s="4"/>
+      <c r="D149" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="E149" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F149" s="7"/>
+      <c r="F149" s="7" t="s">
+        <v>516</v>
+      </c>
       <c r="G149" s="5">
         <v>13</v>
       </c>
@@ -10151,11 +11295,15 @@
       <c r="C150" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D150" s="4"/>
+      <c r="D150" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="E150" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="F150" s="7"/>
+      <c r="F150" s="7" t="s">
+        <v>517</v>
+      </c>
       <c r="G150" s="5">
         <v>14</v>
       </c>
@@ -10204,11 +11352,15 @@
       <c r="C151" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D151" s="4"/>
+      <c r="D151" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="E151" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="F151" s="7"/>
+      <c r="F151" s="7" t="s">
+        <v>518</v>
+      </c>
       <c r="G151" s="5">
         <v>15</v>
       </c>
@@ -10257,11 +11409,15 @@
       <c r="C152" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D152" s="4"/>
+      <c r="D152" s="4" t="s">
+        <v>519</v>
+      </c>
       <c r="E152" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="F152" s="7"/>
+      <c r="F152" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="G152" s="5">
         <v>3</v>
       </c>
@@ -10310,11 +11466,15 @@
       <c r="C153" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D153" s="4"/>
+      <c r="D153" s="4" t="s">
+        <v>519</v>
+      </c>
       <c r="E153" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="F153" s="7"/>
+      <c r="F153" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="G153" s="5">
         <v>1</v>
       </c>
@@ -10363,11 +11523,15 @@
       <c r="C154" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D154" s="4"/>
+      <c r="D154" s="4" t="s">
+        <v>519</v>
+      </c>
       <c r="E154" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="F154" s="7"/>
+      <c r="F154" s="7" t="s">
+        <v>522</v>
+      </c>
       <c r="G154" s="5">
         <v>2</v>
       </c>
@@ -10416,11 +11580,15 @@
       <c r="C155" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D155" s="4"/>
+      <c r="D155" s="4" t="s">
+        <v>519</v>
+      </c>
       <c r="E155" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="F155" s="7"/>
+      <c r="F155" s="7" t="s">
+        <v>523</v>
+      </c>
       <c r="G155" s="5">
         <v>4</v>
       </c>
@@ -10469,11 +11637,15 @@
       <c r="C156" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D156" s="4"/>
+      <c r="D156" s="4" t="s">
+        <v>519</v>
+      </c>
       <c r="E156" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="F156" s="7"/>
+      <c r="F156" s="7" t="s">
+        <v>524</v>
+      </c>
       <c r="G156" s="5">
         <v>5</v>
       </c>
@@ -10522,11 +11694,15 @@
       <c r="C157" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D157" s="4"/>
+      <c r="D157" s="4" t="s">
+        <v>519</v>
+      </c>
       <c r="E157" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F157" s="7"/>
+      <c r="F157" s="7" t="s">
+        <v>525</v>
+      </c>
       <c r="G157" s="5">
         <v>9</v>
       </c>
@@ -10575,11 +11751,15 @@
       <c r="C158" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D158" s="4"/>
+      <c r="D158" s="4" t="s">
+        <v>519</v>
+      </c>
       <c r="E158" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="F158" s="7"/>
+      <c r="F158" s="7" t="s">
+        <v>526</v>
+      </c>
       <c r="G158" s="5">
         <v>6</v>
       </c>
@@ -10628,11 +11808,15 @@
       <c r="C159" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D159" s="4"/>
+      <c r="D159" s="4" t="s">
+        <v>519</v>
+      </c>
       <c r="E159" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="F159" s="7"/>
+      <c r="F159" s="7" t="s">
+        <v>527</v>
+      </c>
       <c r="G159" s="5">
         <v>10</v>
       </c>
@@ -10681,11 +11865,15 @@
       <c r="C160" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D160" s="4"/>
+      <c r="D160" s="4" t="s">
+        <v>519</v>
+      </c>
       <c r="E160" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="F160" s="7"/>
+      <c r="F160" s="7" t="s">
+        <v>528</v>
+      </c>
       <c r="G160" s="5">
         <v>7</v>
       </c>
@@ -10734,11 +11922,15 @@
       <c r="C161" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D161" s="4"/>
+      <c r="D161" s="4" t="s">
+        <v>519</v>
+      </c>
       <c r="E161" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="F161" s="7"/>
+      <c r="F161" s="7" t="s">
+        <v>529</v>
+      </c>
       <c r="G161" s="5">
         <v>8</v>
       </c>
@@ -10787,11 +11979,15 @@
       <c r="C162" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D162" s="4"/>
+      <c r="D162" s="4" t="s">
+        <v>519</v>
+      </c>
       <c r="E162" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="F162" s="7"/>
+      <c r="F162" s="7" t="s">
+        <v>530</v>
+      </c>
       <c r="G162" s="5">
         <v>11</v>
       </c>
@@ -10840,11 +12036,15 @@
       <c r="C163" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D163" s="4"/>
+      <c r="D163" s="4" t="s">
+        <v>519</v>
+      </c>
       <c r="E163" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="F163" s="7"/>
+      <c r="F163" s="7" t="s">
+        <v>531</v>
+      </c>
       <c r="G163" s="5">
         <v>12</v>
       </c>
@@ -10893,11 +12093,15 @@
       <c r="C164" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D164" s="4"/>
+      <c r="D164" s="4" t="s">
+        <v>519</v>
+      </c>
       <c r="E164" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="F164" s="7"/>
+      <c r="F164" s="7" t="s">
+        <v>532</v>
+      </c>
       <c r="G164" s="5">
         <v>13</v>
       </c>
@@ -10946,11 +12150,15 @@
       <c r="C165" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D165" s="4"/>
+      <c r="D165" s="4" t="s">
+        <v>519</v>
+      </c>
       <c r="E165" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="F165" s="7"/>
+      <c r="F165" s="7" t="s">
+        <v>533</v>
+      </c>
       <c r="G165" s="5">
         <v>14</v>
       </c>
@@ -10999,11 +12207,15 @@
       <c r="C166" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D166" s="4"/>
+      <c r="D166" s="4" t="s">
+        <v>519</v>
+      </c>
       <c r="E166" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="F166" s="7"/>
+      <c r="F166" s="7" t="s">
+        <v>534</v>
+      </c>
       <c r="G166" s="5">
         <v>15</v>
       </c>
@@ -11052,11 +12264,15 @@
       <c r="C167" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D167" s="4"/>
+      <c r="D167" s="4" t="s">
+        <v>535</v>
+      </c>
       <c r="E167" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="F167" s="7"/>
+      <c r="F167" s="7" t="s">
+        <v>536</v>
+      </c>
       <c r="G167" s="5">
         <v>2</v>
       </c>
@@ -11105,11 +12321,15 @@
       <c r="C168" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D168" s="4"/>
+      <c r="D168" s="4" t="s">
+        <v>535</v>
+      </c>
       <c r="E168" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="F168" s="7"/>
+      <c r="F168" s="7" t="s">
+        <v>537</v>
+      </c>
       <c r="G168" s="5">
         <v>4</v>
       </c>
@@ -11158,11 +12378,15 @@
       <c r="C169" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D169" s="4"/>
+      <c r="D169" s="4" t="s">
+        <v>535</v>
+      </c>
       <c r="E169" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="F169" s="7"/>
+      <c r="F169" s="7" t="s">
+        <v>538</v>
+      </c>
       <c r="G169" s="5">
         <v>3</v>
       </c>
@@ -11211,11 +12435,15 @@
       <c r="C170" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D170" s="4"/>
+      <c r="D170" s="4" t="s">
+        <v>535</v>
+      </c>
       <c r="E170" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="F170" s="7"/>
+      <c r="F170" s="7" t="s">
+        <v>539</v>
+      </c>
       <c r="G170" s="5">
         <v>7</v>
       </c>
@@ -11264,11 +12492,15 @@
       <c r="C171" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D171" s="4"/>
+      <c r="D171" s="4" t="s">
+        <v>535</v>
+      </c>
       <c r="E171" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F171" s="7"/>
+      <c r="F171" s="7" t="s">
+        <v>540</v>
+      </c>
       <c r="G171" s="5">
         <v>5</v>
       </c>
@@ -11317,11 +12549,15 @@
       <c r="C172" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D172" s="4"/>
+      <c r="D172" s="4" t="s">
+        <v>535</v>
+      </c>
       <c r="E172" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="F172" s="7"/>
+      <c r="F172" s="7" t="s">
+        <v>541</v>
+      </c>
       <c r="G172" s="5">
         <v>1</v>
       </c>
@@ -11370,11 +12606,15 @@
       <c r="C173" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D173" s="4"/>
+      <c r="D173" s="4" t="s">
+        <v>535</v>
+      </c>
       <c r="E173" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="F173" s="7"/>
+      <c r="F173" s="7" t="s">
+        <v>542</v>
+      </c>
       <c r="G173" s="5">
         <v>9</v>
       </c>
@@ -11423,11 +12663,15 @@
       <c r="C174" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D174" s="4"/>
+      <c r="D174" s="4" t="s">
+        <v>535</v>
+      </c>
       <c r="E174" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="F174" s="7"/>
+      <c r="F174" s="7" t="s">
+        <v>543</v>
+      </c>
       <c r="G174" s="5">
         <v>8</v>
       </c>
@@ -11476,11 +12720,15 @@
       <c r="C175" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D175" s="4"/>
+      <c r="D175" s="4" t="s">
+        <v>535</v>
+      </c>
       <c r="E175" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="F175" s="7"/>
+      <c r="F175" s="7" t="s">
+        <v>544</v>
+      </c>
       <c r="G175" s="5">
         <v>6</v>
       </c>
@@ -11529,11 +12777,15 @@
       <c r="C176" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D176" s="4"/>
+      <c r="D176" s="4" t="s">
+        <v>535</v>
+      </c>
       <c r="E176" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="F176" s="7"/>
+      <c r="F176" s="7" t="s">
+        <v>545</v>
+      </c>
       <c r="G176" s="5">
         <v>10</v>
       </c>
@@ -11582,11 +12834,15 @@
       <c r="C177" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D177" s="4"/>
+      <c r="D177" s="4" t="s">
+        <v>535</v>
+      </c>
       <c r="E177" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="F177" s="7"/>
+      <c r="F177" s="7" t="s">
+        <v>546</v>
+      </c>
       <c r="G177" s="5">
         <v>11</v>
       </c>
@@ -11635,11 +12891,15 @@
       <c r="C178" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D178" s="4"/>
+      <c r="D178" s="4" t="s">
+        <v>535</v>
+      </c>
       <c r="E178" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="F178" s="7"/>
+      <c r="F178" s="7" t="s">
+        <v>547</v>
+      </c>
       <c r="G178" s="5">
         <v>13</v>
       </c>
@@ -11688,11 +12948,15 @@
       <c r="C179" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D179" s="4"/>
+      <c r="D179" s="4" t="s">
+        <v>535</v>
+      </c>
       <c r="E179" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="F179" s="7"/>
+      <c r="F179" s="7" t="s">
+        <v>548</v>
+      </c>
       <c r="G179" s="5">
         <v>12</v>
       </c>
@@ -11741,11 +13005,15 @@
       <c r="C180" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D180" s="4"/>
+      <c r="D180" s="4" t="s">
+        <v>535</v>
+      </c>
       <c r="E180" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="F180" s="7"/>
+      <c r="F180" s="7" t="s">
+        <v>549</v>
+      </c>
       <c r="G180" s="5">
         <v>14</v>
       </c>
@@ -11794,11 +13062,15 @@
       <c r="C181" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D181" s="4"/>
+      <c r="D181" s="4" t="s">
+        <v>535</v>
+      </c>
       <c r="E181" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="F181" s="7"/>
+      <c r="F181" s="7" t="s">
+        <v>550</v>
+      </c>
       <c r="G181" s="5">
         <v>15</v>
       </c>
@@ -11847,11 +13119,15 @@
       <c r="C182" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D182" s="4"/>
+      <c r="D182" s="4" t="s">
+        <v>551</v>
+      </c>
       <c r="E182" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="F182" s="7"/>
+      <c r="F182" s="7" t="s">
+        <v>552</v>
+      </c>
       <c r="G182" s="5">
         <v>5</v>
       </c>
@@ -11900,11 +13176,15 @@
       <c r="C183" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D183" s="4"/>
+      <c r="D183" s="4" t="s">
+        <v>551</v>
+      </c>
       <c r="E183" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="F183" s="7"/>
+      <c r="F183" s="7" t="s">
+        <v>553</v>
+      </c>
       <c r="G183" s="5">
         <v>1</v>
       </c>
@@ -11953,11 +13233,15 @@
       <c r="C184" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D184" s="4"/>
+      <c r="D184" s="4" t="s">
+        <v>551</v>
+      </c>
       <c r="E184" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="F184" s="7"/>
+      <c r="F184" s="7" t="s">
+        <v>554</v>
+      </c>
       <c r="G184" s="5">
         <v>2</v>
       </c>
@@ -12006,11 +13290,15 @@
       <c r="C185" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D185" s="4"/>
+      <c r="D185" s="4" t="s">
+        <v>551</v>
+      </c>
       <c r="E185" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="F185" s="7"/>
+      <c r="F185" s="7" t="s">
+        <v>555</v>
+      </c>
       <c r="G185" s="5">
         <v>4</v>
       </c>
@@ -12059,11 +13347,15 @@
       <c r="C186" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D186" s="4"/>
+      <c r="D186" s="4" t="s">
+        <v>551</v>
+      </c>
       <c r="E186" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="F186" s="7"/>
+      <c r="F186" s="7" t="s">
+        <v>556</v>
+      </c>
       <c r="G186" s="5">
         <v>3</v>
       </c>
@@ -12112,11 +13404,15 @@
       <c r="C187" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D187" s="4"/>
+      <c r="D187" s="4" t="s">
+        <v>551</v>
+      </c>
       <c r="E187" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="F187" s="7"/>
+      <c r="F187" s="7" t="s">
+        <v>557</v>
+      </c>
       <c r="G187" s="5">
         <v>9</v>
       </c>
@@ -12165,11 +13461,15 @@
       <c r="C188" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D188" s="4"/>
+      <c r="D188" s="4" t="s">
+        <v>551</v>
+      </c>
       <c r="E188" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="F188" s="7"/>
+      <c r="F188" s="7" t="s">
+        <v>558</v>
+      </c>
       <c r="G188" s="5">
         <v>10</v>
       </c>
@@ -12218,11 +13518,15 @@
       <c r="C189" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D189" s="4"/>
+      <c r="D189" s="4" t="s">
+        <v>551</v>
+      </c>
       <c r="E189" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="F189" s="7"/>
+      <c r="F189" s="7" t="s">
+        <v>559</v>
+      </c>
       <c r="G189" s="5">
         <v>6</v>
       </c>
@@ -12271,11 +13575,15 @@
       <c r="C190" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D190" s="4"/>
+      <c r="D190" s="4" t="s">
+        <v>551</v>
+      </c>
       <c r="E190" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="F190" s="7"/>
+      <c r="F190" s="7" t="s">
+        <v>560</v>
+      </c>
       <c r="G190" s="5">
         <v>7</v>
       </c>
@@ -12324,11 +13632,15 @@
       <c r="C191" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D191" s="4"/>
+      <c r="D191" s="4" t="s">
+        <v>551</v>
+      </c>
       <c r="E191" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="F191" s="7"/>
+      <c r="F191" s="7" t="s">
+        <v>561</v>
+      </c>
       <c r="G191" s="5">
         <v>8</v>
       </c>
@@ -12377,11 +13689,15 @@
       <c r="C192" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D192" s="4"/>
+      <c r="D192" s="4" t="s">
+        <v>551</v>
+      </c>
       <c r="E192" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="F192" s="7"/>
+      <c r="F192" s="7" t="s">
+        <v>562</v>
+      </c>
       <c r="G192" s="5">
         <v>11</v>
       </c>
@@ -12430,11 +13746,15 @@
       <c r="C193" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D193" s="4"/>
+      <c r="D193" s="4" t="s">
+        <v>551</v>
+      </c>
       <c r="E193" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="F193" s="7"/>
+      <c r="F193" s="7" t="s">
+        <v>563</v>
+      </c>
       <c r="G193" s="5">
         <v>12</v>
       </c>
@@ -12483,11 +13803,15 @@
       <c r="C194" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D194" s="4"/>
+      <c r="D194" s="4" t="s">
+        <v>551</v>
+      </c>
       <c r="E194" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="F194" s="7"/>
+      <c r="F194" s="7" t="s">
+        <v>564</v>
+      </c>
       <c r="G194" s="5">
         <v>13</v>
       </c>
@@ -12536,11 +13860,15 @@
       <c r="C195" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D195" s="4"/>
+      <c r="D195" s="4" t="s">
+        <v>551</v>
+      </c>
       <c r="E195" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="F195" s="7"/>
+      <c r="F195" s="7" t="s">
+        <v>565</v>
+      </c>
       <c r="G195" s="5">
         <v>14</v>
       </c>
@@ -12589,11 +13917,15 @@
       <c r="C196" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D196" s="4"/>
+      <c r="D196" s="4" t="s">
+        <v>551</v>
+      </c>
       <c r="E196" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="F196" s="7"/>
+      <c r="F196" s="7" t="s">
+        <v>566</v>
+      </c>
       <c r="G196" s="5">
         <v>15</v>
       </c>
@@ -12642,11 +13974,15 @@
       <c r="C197" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D197" s="4"/>
+      <c r="D197" s="4" t="s">
+        <v>568</v>
+      </c>
       <c r="E197" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="F197" s="7"/>
+      <c r="F197" s="7" t="s">
+        <v>569</v>
+      </c>
       <c r="G197" s="5">
         <v>1</v>
       </c>
@@ -12695,11 +14031,15 @@
       <c r="C198" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D198" s="4"/>
+      <c r="D198" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="E198" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="F198" s="7"/>
+      <c r="F198" s="7" t="s">
+        <v>570</v>
+      </c>
       <c r="G198" s="5">
         <v>6</v>
       </c>
@@ -12748,11 +14088,15 @@
       <c r="C199" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D199" s="4"/>
+      <c r="D199" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="E199" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="F199" s="7"/>
+      <c r="F199" s="7" t="s">
+        <v>571</v>
+      </c>
       <c r="G199" s="5">
         <v>7</v>
       </c>
@@ -12801,11 +14145,15 @@
       <c r="C200" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D200" s="4"/>
+      <c r="D200" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="E200" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="F200" s="7"/>
+      <c r="F200" s="7" t="s">
+        <v>572</v>
+      </c>
       <c r="G200" s="5">
         <v>8</v>
       </c>
@@ -12854,11 +14202,15 @@
       <c r="C201" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D201" s="4"/>
+      <c r="D201" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="E201" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="F201" s="7"/>
+      <c r="F201" s="7" t="s">
+        <v>573</v>
+      </c>
       <c r="G201" s="5">
         <v>5</v>
       </c>
@@ -12907,11 +14259,15 @@
       <c r="C202" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D202" s="4"/>
+      <c r="D202" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="E202" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="F202" s="7"/>
+      <c r="F202" s="7" t="s">
+        <v>574</v>
+      </c>
       <c r="G202" s="5">
         <v>9</v>
       </c>
@@ -12960,11 +14316,15 @@
       <c r="C203" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D203" s="4"/>
+      <c r="D203" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="E203" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="F203" s="7"/>
+      <c r="F203" s="7" t="s">
+        <v>575</v>
+      </c>
       <c r="G203" s="5">
         <v>10</v>
       </c>
@@ -13013,11 +14373,15 @@
       <c r="C204" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D204" s="4"/>
+      <c r="D204" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="E204" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="F204" s="7"/>
+      <c r="F204" s="7" t="s">
+        <v>576</v>
+      </c>
       <c r="G204" s="5">
         <v>2</v>
       </c>
@@ -13066,11 +14430,15 @@
       <c r="C205" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D205" s="4"/>
+      <c r="D205" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="E205" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F205" s="7"/>
+      <c r="F205" s="7" t="s">
+        <v>577</v>
+      </c>
       <c r="G205" s="5">
         <v>3</v>
       </c>
@@ -13119,11 +14487,15 @@
       <c r="C206" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D206" s="4"/>
+      <c r="D206" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="E206" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="F206" s="7"/>
+      <c r="F206" s="7" t="s">
+        <v>578</v>
+      </c>
       <c r="G206" s="5">
         <v>4</v>
       </c>
@@ -13172,11 +14544,15 @@
       <c r="C207" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D207" s="4"/>
+      <c r="D207" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="E207" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="F207" s="7"/>
+      <c r="F207" s="7" t="s">
+        <v>579</v>
+      </c>
       <c r="G207" s="5">
         <v>11</v>
       </c>
@@ -13225,11 +14601,15 @@
       <c r="C208" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D208" s="4"/>
+      <c r="D208" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="E208" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="F208" s="7"/>
+      <c r="F208" s="7" t="s">
+        <v>580</v>
+      </c>
       <c r="G208" s="5">
         <v>12</v>
       </c>
@@ -13278,11 +14658,15 @@
       <c r="C209" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D209" s="4"/>
+      <c r="D209" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="E209" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="F209" s="7"/>
+      <c r="F209" s="7" t="s">
+        <v>581</v>
+      </c>
       <c r="G209" s="5">
         <v>13</v>
       </c>
@@ -13331,11 +14715,15 @@
       <c r="C210" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D210" s="4"/>
+      <c r="D210" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="E210" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="F210" s="7"/>
+      <c r="F210" s="7" t="s">
+        <v>582</v>
+      </c>
       <c r="G210" s="5">
         <v>14</v>
       </c>
@@ -13384,11 +14772,15 @@
       <c r="C211" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D211" s="4"/>
+      <c r="D211" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="E211" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F211" s="7"/>
+      <c r="F211" s="7" t="s">
+        <v>583</v>
+      </c>
       <c r="G211" s="5">
         <v>15</v>
       </c>
@@ -13437,11 +14829,15 @@
       <c r="C212" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D212" s="4"/>
+      <c r="D212" s="4" t="s">
+        <v>584</v>
+      </c>
       <c r="E212" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="F212" s="7"/>
+      <c r="F212" s="7" t="s">
+        <v>585</v>
+      </c>
       <c r="G212" s="5">
         <v>6</v>
       </c>
@@ -13490,11 +14886,15 @@
       <c r="C213" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D213" s="4"/>
+      <c r="D213" s="4" t="s">
+        <v>584</v>
+      </c>
       <c r="E213" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="F213" s="7"/>
+      <c r="F213" s="7" t="s">
+        <v>586</v>
+      </c>
       <c r="G213" s="5">
         <v>2</v>
       </c>
@@ -13543,11 +14943,15 @@
       <c r="C214" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D214" s="4"/>
+      <c r="D214" s="4" t="s">
+        <v>584</v>
+      </c>
       <c r="E214" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="F214" s="7"/>
+      <c r="F214" s="7" t="s">
+        <v>587</v>
+      </c>
       <c r="G214" s="5">
         <v>8</v>
       </c>
@@ -13596,11 +15000,15 @@
       <c r="C215" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D215" s="4"/>
+      <c r="D215" s="4" t="s">
+        <v>584</v>
+      </c>
       <c r="E215" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="F215" s="7"/>
+      <c r="F215" s="7" t="s">
+        <v>588</v>
+      </c>
       <c r="G215" s="5">
         <v>3</v>
       </c>
@@ -13649,11 +15057,15 @@
       <c r="C216" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D216" s="4"/>
+      <c r="D216" s="4" t="s">
+        <v>584</v>
+      </c>
       <c r="E216" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="F216" s="7"/>
+      <c r="F216" s="7" t="s">
+        <v>589</v>
+      </c>
       <c r="G216" s="5">
         <v>1</v>
       </c>
@@ -13702,11 +15114,15 @@
       <c r="C217" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D217" s="4"/>
+      <c r="D217" s="4" t="s">
+        <v>584</v>
+      </c>
       <c r="E217" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="F217" s="7"/>
+      <c r="F217" s="7" t="s">
+        <v>590</v>
+      </c>
       <c r="G217" s="5">
         <v>7</v>
       </c>
@@ -13755,11 +15171,15 @@
       <c r="C218" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D218" s="4"/>
+      <c r="D218" s="4" t="s">
+        <v>584</v>
+      </c>
       <c r="E218" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="F218" s="7"/>
+      <c r="F218" s="7" t="s">
+        <v>591</v>
+      </c>
       <c r="G218" s="5">
         <v>9</v>
       </c>
@@ -13808,11 +15228,15 @@
       <c r="C219" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D219" s="4"/>
+      <c r="D219" s="4" t="s">
+        <v>584</v>
+      </c>
       <c r="E219" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F219" s="7"/>
+      <c r="F219" s="7" t="s">
+        <v>592</v>
+      </c>
       <c r="G219" s="5">
         <v>4</v>
       </c>
@@ -13861,11 +15285,15 @@
       <c r="C220" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D220" s="4"/>
+      <c r="D220" s="4" t="s">
+        <v>584</v>
+      </c>
       <c r="E220" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="F220" s="7"/>
+      <c r="F220" s="7" t="s">
+        <v>593</v>
+      </c>
       <c r="G220" s="5">
         <v>5</v>
       </c>
@@ -13914,11 +15342,15 @@
       <c r="C221" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D221" s="4"/>
+      <c r="D221" s="4" t="s">
+        <v>584</v>
+      </c>
       <c r="E221" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="F221" s="7"/>
+      <c r="F221" s="7" t="s">
+        <v>594</v>
+      </c>
       <c r="G221" s="5">
         <v>10</v>
       </c>
@@ -13967,11 +15399,15 @@
       <c r="C222" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D222" s="4"/>
+      <c r="D222" s="4" t="s">
+        <v>584</v>
+      </c>
       <c r="E222" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="F222" s="7"/>
+      <c r="F222" s="7" t="s">
+        <v>595</v>
+      </c>
       <c r="G222" s="5">
         <v>11</v>
       </c>
@@ -14020,11 +15456,15 @@
       <c r="C223" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D223" s="4"/>
+      <c r="D223" s="4" t="s">
+        <v>584</v>
+      </c>
       <c r="E223" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="F223" s="7"/>
+      <c r="F223" s="7" t="s">
+        <v>596</v>
+      </c>
       <c r="G223" s="5">
         <v>12</v>
       </c>
@@ -14073,11 +15513,15 @@
       <c r="C224" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D224" s="4"/>
+      <c r="D224" s="4" t="s">
+        <v>584</v>
+      </c>
       <c r="E224" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="F224" s="7"/>
+      <c r="F224" s="7" t="s">
+        <v>597</v>
+      </c>
       <c r="G224" s="5">
         <v>13</v>
       </c>
@@ -14126,11 +15570,15 @@
       <c r="C225" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D225" s="4"/>
+      <c r="D225" s="4" t="s">
+        <v>584</v>
+      </c>
       <c r="E225" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="F225" s="7"/>
+      <c r="F225" s="7" t="s">
+        <v>598</v>
+      </c>
       <c r="G225" s="5">
         <v>14</v>
       </c>
@@ -14179,11 +15627,15 @@
       <c r="C226" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D226" s="4"/>
+      <c r="D226" s="4" t="s">
+        <v>584</v>
+      </c>
       <c r="E226" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="F226" s="7"/>
+      <c r="F226" s="7" t="s">
+        <v>599</v>
+      </c>
       <c r="G226" s="5">
         <v>15</v>
       </c>
@@ -14232,11 +15684,15 @@
       <c r="C227" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D227" s="4"/>
+      <c r="D227" s="4" t="s">
+        <v>600</v>
+      </c>
       <c r="E227" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="F227" s="7"/>
+      <c r="F227" s="7" t="s">
+        <v>601</v>
+      </c>
       <c r="G227" s="5">
         <v>5</v>
       </c>
@@ -14285,11 +15741,15 @@
       <c r="C228" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D228" s="4"/>
+      <c r="D228" s="4" t="s">
+        <v>600</v>
+      </c>
       <c r="E228" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="F228" s="7"/>
+      <c r="F228" s="7" t="s">
+        <v>602</v>
+      </c>
       <c r="G228" s="5">
         <v>1</v>
       </c>
@@ -14338,11 +15798,15 @@
       <c r="C229" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D229" s="4"/>
+      <c r="D229" s="4" t="s">
+        <v>600</v>
+      </c>
       <c r="E229" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="F229" s="7"/>
+      <c r="F229" s="7" t="s">
+        <v>603</v>
+      </c>
       <c r="G229" s="5">
         <v>2</v>
       </c>
@@ -14391,11 +15855,15 @@
       <c r="C230" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D230" s="4"/>
+      <c r="D230" s="4" t="s">
+        <v>600</v>
+      </c>
       <c r="E230" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="F230" s="7"/>
+      <c r="F230" s="7" t="s">
+        <v>604</v>
+      </c>
       <c r="G230" s="5">
         <v>3</v>
       </c>
@@ -14444,11 +15912,15 @@
       <c r="C231" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D231" s="4"/>
+      <c r="D231" s="4" t="s">
+        <v>600</v>
+      </c>
       <c r="E231" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="F231" s="7"/>
+      <c r="F231" s="7" t="s">
+        <v>605</v>
+      </c>
       <c r="G231" s="5">
         <v>4</v>
       </c>
@@ -14497,11 +15969,15 @@
       <c r="C232" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D232" s="4"/>
+      <c r="D232" s="4" t="s">
+        <v>600</v>
+      </c>
       <c r="E232" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="F232" s="7"/>
+      <c r="F232" s="7" t="s">
+        <v>615</v>
+      </c>
       <c r="G232" s="5">
         <v>9</v>
       </c>
@@ -14550,11 +16026,15 @@
       <c r="C233" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D233" s="4"/>
+      <c r="D233" s="4" t="s">
+        <v>600</v>
+      </c>
       <c r="E233" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="F233" s="7"/>
+      <c r="F233" s="7" t="s">
+        <v>606</v>
+      </c>
       <c r="G233" s="5">
         <v>10</v>
       </c>
@@ -14603,11 +16083,15 @@
       <c r="C234" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D234" s="4"/>
+      <c r="D234" s="4" t="s">
+        <v>600</v>
+      </c>
       <c r="E234" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="F234" s="7"/>
+      <c r="F234" s="7" t="s">
+        <v>607</v>
+      </c>
       <c r="G234" s="5">
         <v>6</v>
       </c>
@@ -14656,11 +16140,15 @@
       <c r="C235" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D235" s="4"/>
+      <c r="D235" s="4" t="s">
+        <v>600</v>
+      </c>
       <c r="E235" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="F235" s="7"/>
+      <c r="F235" s="7" t="s">
+        <v>608</v>
+      </c>
       <c r="G235" s="5">
         <v>8</v>
       </c>
@@ -14709,11 +16197,15 @@
       <c r="C236" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D236" s="4"/>
+      <c r="D236" s="4" t="s">
+        <v>600</v>
+      </c>
       <c r="E236" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="F236" s="7"/>
+      <c r="F236" s="7" t="s">
+        <v>609</v>
+      </c>
       <c r="G236" s="5">
         <v>7</v>
       </c>
@@ -14762,11 +16254,15 @@
       <c r="C237" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D237" s="4"/>
+      <c r="D237" s="4" t="s">
+        <v>600</v>
+      </c>
       <c r="E237" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="F237" s="7"/>
+      <c r="F237" s="7" t="s">
+        <v>610</v>
+      </c>
       <c r="G237" s="5">
         <v>11</v>
       </c>
@@ -14815,11 +16311,15 @@
       <c r="C238" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D238" s="4"/>
+      <c r="D238" s="4" t="s">
+        <v>600</v>
+      </c>
       <c r="E238" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="F238" s="7"/>
+      <c r="F238" s="7" t="s">
+        <v>611</v>
+      </c>
       <c r="G238" s="5">
         <v>12</v>
       </c>
@@ -14868,11 +16368,15 @@
       <c r="C239" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D239" s="4"/>
+      <c r="D239" s="4" t="s">
+        <v>600</v>
+      </c>
       <c r="E239" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="F239" s="7"/>
+      <c r="F239" s="7" t="s">
+        <v>612</v>
+      </c>
       <c r="G239" s="5">
         <v>13</v>
       </c>
@@ -14921,11 +16425,15 @@
       <c r="C240" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D240" s="4"/>
+      <c r="D240" s="4" t="s">
+        <v>600</v>
+      </c>
       <c r="E240" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="F240" s="7"/>
+      <c r="F240" s="7" t="s">
+        <v>613</v>
+      </c>
       <c r="G240" s="5">
         <v>14</v>
       </c>
@@ -14974,11 +16482,15 @@
       <c r="C241" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D241" s="4"/>
+      <c r="D241" s="4" t="s">
+        <v>600</v>
+      </c>
       <c r="E241" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="F241" s="7"/>
+      <c r="F241" s="7" t="s">
+        <v>614</v>
+      </c>
       <c r="G241" s="5">
         <v>15</v>
       </c>
@@ -15027,11 +16539,15 @@
       <c r="C242" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D242" s="4"/>
+      <c r="D242" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="E242" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="F242" s="7"/>
+      <c r="F242" s="7" t="s">
+        <v>440</v>
+      </c>
       <c r="G242" s="5">
         <v>2</v>
       </c>
@@ -15080,11 +16596,15 @@
       <c r="C243" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D243" s="4"/>
+      <c r="D243" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="E243" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="F243" s="7"/>
+      <c r="F243" s="7" t="s">
+        <v>441</v>
+      </c>
       <c r="G243" s="5">
         <v>3</v>
       </c>
@@ -15133,11 +16653,15 @@
       <c r="C244" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D244" s="4"/>
+      <c r="D244" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="E244" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="F244" s="7"/>
+      <c r="F244" s="7" t="s">
+        <v>442</v>
+      </c>
       <c r="G244" s="5">
         <v>4</v>
       </c>
@@ -15186,11 +16710,15 @@
       <c r="C245" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D245" s="4"/>
+      <c r="D245" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="E245" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="F245" s="7"/>
+      <c r="F245" s="7" t="s">
+        <v>443</v>
+      </c>
       <c r="G245" s="5">
         <v>1</v>
       </c>
@@ -15239,11 +16767,15 @@
       <c r="C246" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D246" s="4"/>
+      <c r="D246" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="E246" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="F246" s="7"/>
+      <c r="F246" s="7" t="s">
+        <v>444</v>
+      </c>
       <c r="G246" s="5">
         <v>5</v>
       </c>
@@ -15292,11 +16824,15 @@
       <c r="C247" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D247" s="4"/>
+      <c r="D247" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="E247" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="F247" s="7"/>
+      <c r="F247" s="7" t="s">
+        <v>445</v>
+      </c>
       <c r="G247" s="5">
         <v>6</v>
       </c>
@@ -15345,11 +16881,15 @@
       <c r="C248" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D248" s="4"/>
+      <c r="D248" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="E248" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="F248" s="7"/>
+      <c r="F248" s="7" t="s">
+        <v>446</v>
+      </c>
       <c r="G248" s="5">
         <v>7</v>
       </c>
@@ -15398,11 +16938,15 @@
       <c r="C249" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D249" s="4"/>
+      <c r="D249" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="E249" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="F249" s="7"/>
+      <c r="F249" s="7" t="s">
+        <v>447</v>
+      </c>
       <c r="G249" s="5">
         <v>8</v>
       </c>
@@ -15451,11 +16995,15 @@
       <c r="C250" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D250" s="4"/>
+      <c r="D250" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="E250" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="F250" s="7"/>
+      <c r="F250" s="7" t="s">
+        <v>448</v>
+      </c>
       <c r="G250" s="5">
         <v>9</v>
       </c>
@@ -15504,11 +17052,15 @@
       <c r="C251" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D251" s="4"/>
+      <c r="D251" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="E251" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="F251" s="7"/>
+      <c r="F251" s="7" t="s">
+        <v>449</v>
+      </c>
       <c r="G251" s="5">
         <v>10</v>
       </c>
@@ -15557,11 +17109,15 @@
       <c r="C252" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D252" s="4"/>
+      <c r="D252" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="E252" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="F252" s="7"/>
+      <c r="F252" s="7" t="s">
+        <v>450</v>
+      </c>
       <c r="G252" s="5">
         <v>11</v>
       </c>
@@ -15610,11 +17166,15 @@
       <c r="C253" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D253" s="4"/>
+      <c r="D253" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="E253" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="F253" s="7"/>
+      <c r="F253" s="7" t="s">
+        <v>451</v>
+      </c>
       <c r="G253" s="5">
         <v>12</v>
       </c>
@@ -15663,11 +17223,15 @@
       <c r="C254" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D254" s="4"/>
+      <c r="D254" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="E254" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="F254" s="7"/>
+      <c r="F254" s="7" t="s">
+        <v>452</v>
+      </c>
       <c r="G254" s="5">
         <v>13</v>
       </c>
@@ -15716,11 +17280,15 @@
       <c r="C255" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D255" s="4"/>
+      <c r="D255" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="E255" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="F255" s="7"/>
+      <c r="F255" s="7" t="s">
+        <v>453</v>
+      </c>
       <c r="G255" s="5">
         <v>14</v>
       </c>
@@ -15769,11 +17337,15 @@
       <c r="C256" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D256" s="4"/>
+      <c r="D256" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="E256" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="F256" s="7"/>
+      <c r="F256" s="7" t="s">
+        <v>454</v>
+      </c>
       <c r="G256" s="5">
         <v>15</v>
       </c>
@@ -15822,11 +17394,15 @@
       <c r="C257" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D257" s="4"/>
+      <c r="D257" s="4" t="s">
+        <v>616</v>
+      </c>
       <c r="E257" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="F257" s="7"/>
+      <c r="F257" s="7" t="s">
+        <v>617</v>
+      </c>
       <c r="G257" s="5">
         <v>8</v>
       </c>
@@ -15875,11 +17451,15 @@
       <c r="C258" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D258" s="4"/>
+      <c r="D258" s="4" t="s">
+        <v>616</v>
+      </c>
       <c r="E258" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="F258" s="7"/>
+      <c r="F258" s="7" t="s">
+        <v>618</v>
+      </c>
       <c r="G258" s="5">
         <v>7</v>
       </c>
@@ -15928,11 +17508,15 @@
       <c r="C259" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D259" s="4"/>
+      <c r="D259" s="4" t="s">
+        <v>616</v>
+      </c>
       <c r="E259" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="F259" s="7"/>
+      <c r="F259" s="7" t="s">
+        <v>619</v>
+      </c>
       <c r="G259" s="5">
         <v>1</v>
       </c>
@@ -15981,11 +17565,15 @@
       <c r="C260" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D260" s="4"/>
+      <c r="D260" s="4" t="s">
+        <v>616</v>
+      </c>
       <c r="E260" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="F260" s="7"/>
+      <c r="F260" s="7" t="s">
+        <v>620</v>
+      </c>
       <c r="G260" s="5">
         <v>9</v>
       </c>
@@ -16034,11 +17622,15 @@
       <c r="C261" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D261" s="4"/>
+      <c r="D261" s="4" t="s">
+        <v>616</v>
+      </c>
       <c r="E261" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="F261" s="7"/>
+      <c r="F261" s="7" t="s">
+        <v>621</v>
+      </c>
       <c r="G261" s="5">
         <v>2</v>
       </c>
@@ -16087,11 +17679,15 @@
       <c r="C262" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D262" s="4"/>
+      <c r="D262" s="4" t="s">
+        <v>616</v>
+      </c>
       <c r="E262" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="F262" s="7"/>
+      <c r="F262" s="7" t="s">
+        <v>622</v>
+      </c>
       <c r="G262" s="5">
         <v>3</v>
       </c>
@@ -16140,11 +17736,15 @@
       <c r="C263" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D263" s="4"/>
+      <c r="D263" s="4" t="s">
+        <v>616</v>
+      </c>
       <c r="E263" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="F263" s="7"/>
+      <c r="F263" s="7" t="s">
+        <v>623</v>
+      </c>
       <c r="G263" s="5">
         <v>4</v>
       </c>
@@ -16193,11 +17793,15 @@
       <c r="C264" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D264" s="4"/>
+      <c r="D264" s="4" t="s">
+        <v>616</v>
+      </c>
       <c r="E264" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="F264" s="7"/>
+      <c r="F264" s="7" t="s">
+        <v>624</v>
+      </c>
       <c r="G264" s="5">
         <v>5</v>
       </c>
@@ -16246,11 +17850,15 @@
       <c r="C265" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D265" s="4"/>
+      <c r="D265" s="4" t="s">
+        <v>616</v>
+      </c>
       <c r="E265" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="F265" s="7"/>
+      <c r="F265" s="7" t="s">
+        <v>625</v>
+      </c>
       <c r="G265" s="5">
         <v>6</v>
       </c>
@@ -16299,11 +17907,15 @@
       <c r="C266" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D266" s="4"/>
+      <c r="D266" s="4" t="s">
+        <v>616</v>
+      </c>
       <c r="E266" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="F266" s="7"/>
+      <c r="F266" s="7" t="s">
+        <v>626</v>
+      </c>
       <c r="G266" s="5">
         <v>10</v>
       </c>
@@ -16352,11 +17964,15 @@
       <c r="C267" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D267" s="4"/>
+      <c r="D267" s="4" t="s">
+        <v>616</v>
+      </c>
       <c r="E267" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="F267" s="7"/>
+      <c r="F267" s="7" t="s">
+        <v>627</v>
+      </c>
       <c r="G267" s="5">
         <v>11</v>
       </c>
@@ -16405,11 +18021,15 @@
       <c r="C268" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D268" s="4"/>
+      <c r="D268" s="4" t="s">
+        <v>616</v>
+      </c>
       <c r="E268" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="F268" s="7"/>
+      <c r="F268" s="7" t="s">
+        <v>628</v>
+      </c>
       <c r="G268" s="5">
         <v>12</v>
       </c>
@@ -16458,11 +18078,15 @@
       <c r="C269" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D269" s="4"/>
+      <c r="D269" s="4" t="s">
+        <v>616</v>
+      </c>
       <c r="E269" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="F269" s="7"/>
+      <c r="F269" s="7" t="s">
+        <v>629</v>
+      </c>
       <c r="G269" s="5">
         <v>13</v>
       </c>
@@ -16511,11 +18135,15 @@
       <c r="C270" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D270" s="4"/>
+      <c r="D270" s="4" t="s">
+        <v>616</v>
+      </c>
       <c r="E270" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="F270" s="7"/>
+      <c r="F270" s="7" t="s">
+        <v>630</v>
+      </c>
       <c r="G270" s="5">
         <v>14</v>
       </c>
@@ -16564,11 +18192,15 @@
       <c r="C271" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D271" s="4"/>
+      <c r="D271" s="4" t="s">
+        <v>616</v>
+      </c>
       <c r="E271" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="F271" s="7"/>
+      <c r="F271" s="7" t="s">
+        <v>631</v>
+      </c>
       <c r="G271" s="5">
         <v>15</v>
       </c>
